--- a/YouTube이슈분석_개인채널_2026-07-10.xlsx
+++ b/YouTube이슈분석_개인채널_2026-07-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="351">
   <si>
     <t>날짜</t>
   </si>
@@ -92,10 +92,10 @@
     <t>14:35</t>
   </si>
   <si>
-    <t>한국을 처음 방문한 영국인 부부가 경주를 여행하며 경험한 따뜻한 환대와 한국인들의 친절함을 소개하는 영상입니다. 그들은 예상치 못한 현지인들의 배려와 무관심한 듯하면서도 필요한 도움을 주는 한국 특유의 매력에 깊은 감동을 받았으며, 이를 통해 대한민국의 진짜 모습과 여행의 즐거움을 시청자들에게 전달합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목의 '무관심'이라는 단어는 자극적인 클릭베이트이며, 실제 내용은 한국인의 따뜻한 친절함에 대한 외국인 부부의 긍정적인 경험담입니다.</t>
+    <t>한국을 처음 방문한 영국인 부부가 경주를 여행하며 경험한 따뜻한 사례를 다룹니다. 이들은 한국인들의 낯선 외국인에 대한 세심한 배려와 친절에 깊은 감동을 받았으며, 이러한 한국 특유의 정과 환대 문화가 어떻게 그들의 여행을 특별하게 만들었는지 생생하게 전달합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 달리 실제 내용은 한국의 친절한 문화를 칭찬하는 긍정적인 여행 후기 영상입니다.</t>
   </si>
   <si>
     <t>▶</t>
@@ -104,24 +104,6 @@
     <t>메타데이터+자막(Gemini)</t>
   </si>
   <si>
-    <t>40m로 소문난 덕풍계곡 수영 도전한 미국 상여자 외국인 #외국인반응 #외국인 #korea</t>
-  </si>
-  <si>
-    <t>미국상여자</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>유튜브 채널 미국상여자가 한국의 숨겨진 명소인 덕풍계곡 제2용소를 방문하여 40m 깊이라는 소문의 진실을 직접 확인하는 과정을 담았습니다. 수려한 자연 경관을 배경으로 외국인 출연자가 계곡 수영에 도전하며 한국 자연의 매력을 체험하고, 실제 깊이에 대한 궁금증을 풀어가는 재미를 선사합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 실제 깊이와 소문 사이의 차이를 확인하기 위해 방문 전 현지 안전 요원의 정보를 참고하는 것이 좋습니다.</t>
-  </si>
-  <si>
     <t>[해외 반응] “칠레 BTS 투어 취소 발표에 펼쳐진 대규모 시위” BTS투어 취소 발표에 일어난 20만 아미들 상황?!</t>
   </si>
   <si>
@@ -131,10 +113,28 @@
     <t>11:34</t>
   </si>
   <si>
-    <t>칠레 정부가 10월 예정된 BTS 산티아고 국립경기장 공연을 잔디 훼손 명분으로 갑작스럽게 불허하자, 20만 명의 아미들이 강력히 반발하며 대통령궁 앞 대규모 시위를 벌였습니다. 팬들은 과거 타 가수 공연과의 형평성을 지적하며 직접 잔디를 보수하겠다는 의지까지 보이는 등 거센 항의가 이어지고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️본 영상은 자극적인 제목과 내용을 바탕으로 제작된 클릭베이트성 콘텐츠이므로 사실 여부를 교차 검증하며 시청하는 것이 좋습니다.</t>
+    <t>칠레 정부가 10월로 예정된 BTS 산티아고 국립경기장 공연을 잔디 훼손 우려를 이유로 돌연 불허했습니다. 이미 20만 장의 티켓이 매진되고 해외 팬들의 여행 예약까지 마친 상황에서 정부의 결정에 분노한 아미들이 대통령궁 앞에서 대규모 시위를 벌이며 강력히 반발하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 본 영상은 자극적인 제목과 내용을 바탕으로 한 조회수 유도 목적의 콘텐츠이므로 실제 사실관계를 교차 검증할 필요가 있습니다.</t>
+  </si>
+  <si>
+    <t>유럽..한국의 이것까지 살 줄은 몰랐다..폭염에 한국 제품들,이 3가지까지 찾고 있는 이유</t>
+  </si>
+  <si>
+    <t>지구본 뉴스</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>9:43</t>
+  </si>
+  <si>
+    <t>최근 유럽의 기록적인 폭염으로 인해 현지에서 한국산 냉방 가전 및 관련 제품들에 대한 수요가 급증하고 있습니다. 특히 한국 제품의 성능과 실용성이 주목받으며, 유럽 소비자들이 한국의 특정 냉방 관련 3가지 제품을 적극적으로 찾는 현상을 다룬 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 유튜브 제목과 썸네일에서 강조하는 '3가지 물건'에 대한 구체적인 정보는 영상 본문에서 확인이 필요하며, 자극적인 제목의 클릭베이트성 콘텐츠일 가능성을 염두에 두고 시청하는 것이 좋습니다.</t>
   </si>
   <si>
     <t>돈</t>
@@ -149,40 +149,112 @@
     <t>16:48</t>
   </si>
   <si>
-    <t>존 리 대표는 대출금 상환과 투자 사이에서 고민하는 이들에게 감정이 아닌 금리 비교를 통한 객관적 접근을 강조합니다. 소비성 나쁜 부채와 투자성 좋은 부채를 구분하고, 단기적인 학원비 지출 대신 장기적인 복리 투자를 통해 자녀와 미래를 위한 자산 형성을 실천하라는 재정적 지침을 제시합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 무조건적인 빚 상환보다는 대출 이자율과 투자 기대 수익률을 비교하여 자산 증식을 우선순위에 두는 전략적 판단이 필요합니다.</t>
-  </si>
-  <si>
-    <t>반도체 사이클, 이제 판이 바뀝니다! 하반기 삼성전자·SK하이닉스 투자 전략은?</t>
-  </si>
-  <si>
-    <t>딜사이트경제TV</t>
-  </si>
-  <si>
-    <t>14:06</t>
-  </si>
-  <si>
-    <t>본 영상은 반도체 산업의 새로운 사이클 도래에 따른 시장 환경 변화와 하반기 삼성전자 및 SK하이닉스의 투자 전략을 분석합니다. 업황 변동성에 대응하기 위해 반도체 시장의 흐름과 향후 주가 전망을 다각도로 점검하며 투자자들에게 객관적인 시장 관점을 제시합니다.</t>
-  </si>
-  <si>
-    <t>반도체주는 글로벌 경기와 수급에 민감하므로 단기 등락보다는 HBM 등 핵심 기술 경쟁력을 중심으로 한 장기적인 관점의 접근이 필요합니다.</t>
-  </si>
-  <si>
-    <t>TSMC 비상! 주문 폭주한 삼성전자, 내년 공정 물량까지 완판됐다</t>
-  </si>
-  <si>
-    <t>서울경제TV</t>
-  </si>
-  <si>
-    <t>7:03</t>
-  </si>
-  <si>
-    <t>삼성전자가 파운드리 분야에서 TSMC의 대안으로 급부상하며 AI 반도체 주문이 폭주하고 있습니다. 첨단 공정 물량이 내년까지 완판될 정도로 수주가 이어지고 있어, 글로벌 파운드리 시장 내 삼성전자의 점유율 확대와 수익성 개선이 기대되는 상황을 분석합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목의 '내년 물량 완판'은 시장의 기대감을 반영한 과장된 표현일 수 있으므로, 실제 수주 공시와 공식적인 실적 발표를 교차 검증하는 신중한 접근이 필요합니다.</t>
+    <t>본 영상은 대출 상환과 투자 사이에서 고민하는 이들을 위해 금융 전문가 존리가 올바른 부채 관리와 장기 투자의 중요성을 설명합니다. 소비성 부채는 즉시 청산하되, 생산적 자산을 위한 좋은 부채는 전략적으로 활용하며 복리의 마법을 누리는 투자를 지속할 것을 강조합니다. 단순히 빚을 갚는 데 급급하기보다 자신의 금융 건강 상태를 점검하고 자녀에게도 자본주의 교육을 실천하는 라이프스타일의 변화를 주문합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 빚을 무조건 갚는 것이 정답은 아니며, 대출 금리와 투자 수익률을 비교해 더 높은 기대 수익을 낼 수 있는 곳에 자금을 운용하는 것이 경제적으로 현명합니다.</t>
+  </si>
+  <si>
+    <t>일본사람들이 주식을 사고 싶어도 못 사는 이유</t>
+  </si>
+  <si>
+    <t>ぱく家(박가네)</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>일본에 거주하는 한일 부부 유튜버 박가네가 일본 현지인의 시선에서 일본의 사회, 경제, 문화를 깊이 있게 다루는 영상입니다. 특히 한국인들이 궁금해할 만한 일본의 경제적 특징이나 주식 시장과 관련된 일본만의 독특한 환경, 제도적 배경 등을 현지 경험을 바탕으로 알기 쉽게 설명해 줍니다.</t>
+  </si>
+  <si>
+    <t>⚠️일본 현지인이 전하는 경제 문화 정보는 한국과는 다른 구조적 요인을 이해하는 데 도움을 줍니다.</t>
+  </si>
+  <si>
+    <t>반도체 vs 빅테크, 투자 대가들은 먼저 움직였다!</t>
+  </si>
+  <si>
+    <t>수페TV</t>
+  </si>
+  <si>
+    <t>19:12</t>
+  </si>
+  <si>
+    <t>본 영상은 반도체에서 빅테크, AI 클라우드로 이동하는 투자 중심축의 변화를 다룹니다. 시장의 과열을 경계하며 냉철한 점검의 필요성을 강조하고, 2026년 하반기까지 이어질 투자 로드맵과 미국 ETF 전략을 통해 장기적인 관점에서의 현명한 투자 방향을 제시합니다.</t>
+  </si>
+  <si>
+    <t>AI 산업의 흐름이 급변하는 시기일수록 흥분을 가라앉히고 객관적인 데이터를 바탕으로 투자 포트폴리오를 점검해야 합니다.</t>
+  </si>
+  <si>
+    <t>여행</t>
+  </si>
+  <si>
+    <t>한국 여행에 온 일본인이 한국인의 따뜻함에 눈물이 나올것 같았어요...</t>
+  </si>
+  <si>
+    <t>리코짱</t>
+  </si>
+  <si>
+    <t>9:28</t>
+  </si>
+  <si>
+    <t>일본인 유튜버 리코짱이 한국 여행 중 경험한 현지인들과의 따뜻한 교류와 감동적인 에피소드를 다룬 영상입니다. 한국인의 친절함에 깊은 인상을 받은 리코짱이 음식과 문화를 즐기며 느끼는 진솔한 감정을 공유하며, 한국 여행의 매력을 따뜻한 시선으로 담아내어 시청자들에게 힐링을 선사합니다.</t>
+  </si>
+  <si>
+    <t>⚠️본 영상은 감성적인 경험을 강조하는 클릭베이트 형식의 제목을 사용하고 있으므로, 객관적인 정보보다는 여행의 분위기와 감동적인 사연 위주의 콘텐츠임을 참고하시기 바랍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일본에 살인적인 여름에도 에어컨을 못 켜는 이유. 전기 요금 절약 하려면 비싼 에어컨을 바꾸라는데.. </t>
+  </si>
+  <si>
+    <t>Kim’s 일본 일상 vlog</t>
+  </si>
+  <si>
+    <t>15:28</t>
+  </si>
+  <si>
+    <t>일본의 기록적인 폭염 속에서도 치솟는 전기 요금으로 인해 에어컨 사용을 망설이는 현지 상황을 다룹니다. 특히 노후된 에어컨의 높은 전력 소비 문제를 해결하기 위해 고효율 신형 모델로의 교체가 권장되지만, 초기 비용 부담과 관련한 한일 부부의 현실적인 고민과 일상적인 대처 방법을 공유하는 브이로그 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 전기 요금 절감을 위해 구형 에어컨을 신형으로 바꾸는 것은 장기적 관점에서는 효율적이나 초기 투자 비용이 크므로 본인의 거주 환경과 사용 시간을 고려해 결정해야 합니다.</t>
+  </si>
+  <si>
+    <t>고백 받기 2일 전 떠난 나홀로 호캉스 브이로그</t>
+  </si>
+  <si>
+    <t>다인이공</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>16:53</t>
+  </si>
+  <si>
+    <t>유튜버 다인이공이 고백을 받기 이틀 전, 혼자만의 시간을 갖기 위해 떠난 호캉스 브이로그 영상입니다. 일상 속 여유를 즐기는 모습과 함께 광고 제품인 일리윤 선로션을 소개하며, 설레는 이벤트 전 호캉스를 통해 힐링하는 브이로그 콘텐츠를 담고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 고백을 암시하는 제목으로 시청자의 호기심을 유발하는 브이로그 형식의 감성 광고 영상입니다.</t>
+  </si>
+  <si>
+    <t>e스포츠</t>
+  </si>
+  <si>
+    <t>18연승중이라길래 들어가봤는데 알고봤더니 상대가 프로게이머!!? 대체 누구지??</t>
+  </si>
+  <si>
+    <t>[ALTUBE] 김성현TV</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>스타크래프트 전 프로게이머 김성현(알파고)이 래더 게임 중 18연승 중인 상대를 만나 치열한 대결을 펼치는 영상입니다. 상대가 단순한 일반인이 아닌 실력자임을 직감한 김성현이 노련한 운영으로 경기를 풀어나가는 과정과, 게임 후 상대 정체를 확인하며 벌어지는 흥미로운 상황을 담았습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 클릭베이트 성격이 강한 제목이지만, 전 프로게이머의 수준 높은 판단력과 미세한 컨트롤 차이를 확인하고 싶은 팬들에게 유익한 경기 영상입니다.</t>
   </si>
   <si>
     <t>연애</t>
@@ -194,133 +266,316 @@
     <t>수쩡민</t>
   </si>
   <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
     <t>10:45</t>
   </si>
   <si>
-    <t>유튜버 수쩡민이 드디어 연애를 시작했다는 소식을 알리며, 이를 기념해 구독자들의 연애 고민을 들어주고 조언을 건네는 상담 콘텐츠입니다. 본인의 실제 연애 경험과 감정을 공유하며 시청자와 더욱 친밀하게 소통하고 공감대를 형성하는 시간을 가집니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 연애 시작이라는 자극적인 키워드로 호기심을 유발하지만, 실제 내용은 구독자와의 소통 중심적인 Q&amp;A 상담 영상입니다.</t>
+    <t>유튜버 수쩡민이 드디어 연애를 시작하게 된 소식을 알리며, 구독자들과 함께 연애에 관한 고민과 사연을 나누는 Q&amp;A 형태의 영상입니다. 본인의 행복한 근황 공유와 더불어 시청자들의 다양한 연애 경험담 및 고민에 대해 진솔하고 현실적인 조언을 건네며 소통의 시간을 가집니다.</t>
+  </si>
+  <si>
+    <t>연애를 시작하며 느낀 감정과 타인의 연애 고민을 통해 건강한 관계 형성에 필요한 마음가짐을 배울 수 있습니다.</t>
+  </si>
+  <si>
+    <t>라이프</t>
+  </si>
+  <si>
+    <t>10년 준비한 CPA 시험 포기, 엄마에게 전화를 걸었습니다.(통화장면녹화)</t>
+  </si>
+  <si>
+    <t>안규먼트</t>
+  </si>
+  <si>
+    <t>6:08</t>
+  </si>
+  <si>
+    <t>10년 동안 모든 청춘을 바쳤던 CPA 수험생활을 마치고 새로운 도전을 시작하는 작성자의 심경을 담은 영상입니다. 오랜 고시 생활로 인한 조급함을 뒤로하고 타인의 시선에서 벗어나 담담하게 자신의 삶을 새로 꾸려나가겠다는 다짐을 전하며, 수험생 시절의 노력을 밑거름 삼아 성장해 나갈 미래를 예고합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 장기적인 수험 생활에 지쳤을 때, 자신의 인생을 새로운 방향으로 전환하는 용기와 자기 객관화에 대한 인사이트를 얻을 수 있습니다.</t>
+  </si>
+  <si>
+    <t>[SUB] 슨뇽 대전 빵 엄청 먹여주는 날</t>
+  </si>
+  <si>
+    <t>민와와</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>민와와가 특별 게스트 승용과 함께 대전으로 떠난 빵지순례 브이로그입니다. 평소 가보고 싶었던 유명 빵집들을 방문하며 하루 종일 맛있는 빵을 먹고 즐기는 자연스러운 일상을 담았습니다. 대전의 맛집들을 탐방하며 두 사람이 나누는 소소한 대화와 행복한 먹방 모습을 통해 랜선 여행의 즐거움을 느낄 수 있는 영상입니다.</t>
+  </si>
+  <si>
+    <t>대전 빵 투어 계획 시 유명 빵집의 웨이팅 시간을 고려하여 효율적인 동선을 미리 파악하는 것이 중요합니다.</t>
+  </si>
+  <si>
+    <t>매니저 오리고기 첫 브이로그</t>
+  </si>
+  <si>
+    <t>오리고기 ORIGOGI</t>
+  </si>
+  <si>
+    <t>5:52</t>
+  </si>
+  <si>
+    <t>버튜버 그룹 프로젝트아이의 매니저 오리고기가 현대백화점 신촌점 U-PLEX에서 진행되는 팝업 스토어 현장을 담은 첫 브이로그입니다. 2026년 7월 10일부터 7월 16일까지 운영되는 이번 팝업의 주요 장소와 팬들이 확인할 수 있는 공지처를 상세히 안내하고 있습니다.</t>
+  </si>
+  <si>
+    <t>팝업 스토어의 상세한 행사 일정과 공지 사항은 공식 팬카페와 공식 X(트위터) 계정을 통해 확인하는 것이 가장 정확합니다.</t>
   </si>
   <si>
     <t>일본</t>
   </si>
   <si>
-    <t>【山本由伸】7回10奪三振無失点の圧巻投球！サイ・ヤング級の投球にレジェンド絶句</t>
-  </si>
-  <si>
-    <t>大谷解説TV</t>
+    <t>【海外の反応】興味本位で見たらとんでもない作品に出合ったニキ【のび太＆ジャイアン＆スネ夫 - もらいもん feat.しずか with 出木杉 / THE FIRST TAKE】</t>
+  </si>
+  <si>
+    <t>アニメ・歌のリアクション【海外の反応】</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>본 영상은 유튜브 채널 'THE FIRST TAKE'에 공개된 도라에몽 캐릭터(노비타, 자이언, 스네오 등)의 노래 '모라이몬'에 대한 해외 시청자들의 반응을 담고 있습니다. 단순한 호기심으로 시청했다가 곡의 예술성과 완성도에 깊은 감명을 받은 외국인들의 반응을 집중적으로 조명하며, 애니메이션 캐릭터들이 보여준 반전 매력을 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 실제 아티스트가 부르는 일반적인 THE FIRST TAKE 영상과는 성격이 다른 애니메이션 캐릭터 기반의 오리지널 콘텐츠임을 인지하고 감상하세요.</t>
+  </si>
+  <si>
+    <t>【大谷翔平】山本由伸の師匠にド軍が弟子入り殺到「このおじさんヤバすぎる」矢田メソッドでベッツ＆マンシー覚醒…シーハン復活に感謝【海外の反応/MLB】</t>
+  </si>
+  <si>
+    <t>Shohei Chronicle</t>
+  </si>
+  <si>
+    <t>18:34</t>
+  </si>
+  <si>
+    <t>야마모토 요시노부의 신뢰를 받는 트레이너 야다 선생이 LA 다저스 선수들에게 큰 영향을 미치고 있습니다. 야다 메소드는 무키 베츠, 맥스 먼시 등 주축 선수들의 타격감과 에멧 시핸의 투구 밸런스를 개선하며 팀 전체에 '신체의 연결성'이라는 새로운 변화를 가져왔습니다. 본 영상은 야다 선생의 지도가 어떻게 다저스 선수들의 기량 회복과 성적 향상에 기여했는지를 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 선수들의 과학적 교정법을 다루지만, 영상 제작자의 독자적인 해석과 연출이 포함된 엔터테인먼트 콘텐츠임을 인지하고 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>これは素晴らしい文化だよ！日本の立ち飲み屋に外国人観光客が大ウケ</t>
+  </si>
+  <si>
+    <t>黄金のジパング</t>
+  </si>
+  <si>
+    <t>10:49</t>
+  </si>
+  <si>
+    <t>이 영상은 교토의 대표적 명소인 니시키 시장을 방문한 외국인 관광객들이 일본 특유의 '타치노미(서서 마시는 술집)' 문화를 경험하며 느끼는 신선한 즐거움과 감동을 담고 있습니다. 서서 술과 안주를 즐기며 현지인들과 자연스럽게 어우러지는 독특한 분위기는 일본을 방문한 외국인들에게 잊지 못할 특별한 추억이자 매력적인 일본 문화로 깊은 인상을 남기고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 타치노미는 현지인과의 교류가 잦은 곳이므로 일본의 술자리 예절을 가볍게 익히고 가면 더욱 즐거운 경험이 됩니다.</t>
+  </si>
+  <si>
+    <t>【外国株投資家は要注意】驚きの最高裁判決。為替差益課税の落とし穴。</t>
+  </si>
+  <si>
+    <t>ガーコちゃんねる</t>
+  </si>
+  <si>
+    <t>17:47</t>
+  </si>
+  <si>
+    <t>본 영상은 외국 주식 투자자가 주의해야 할 최근 일본 대법원 판결과 그에 따른 환차익 과세 문제를 다룹니다. 특히 해외 주식 투자 시 발생할 수 있는 세무 리스크와 복잡한 세법의 함정을 경고하며, 투자자가 반드시 알아야 할 법적 변화와 실질적인 대응책을 전문가적인 관점에서 상세히 설명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️외국 주식 투자 시 발생하는 환차익은 과세 대상이 될 수 있으므로, 최신 세법 변화와 대법원 판결 내용을 반드시 숙지하여 절세 계획을 세워야 합니다.</t>
+  </si>
+  <si>
+    <t>特定口座で運用している人は早めに確認してください。NISAへ移すべき人とそのままでいい人の違いを解説！</t>
+  </si>
+  <si>
+    <t>鳥海翔の騙されない金融学</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>특정계좌에서 자산을 운용 중인 투자자가 NISA 계좌로 자산을 이전해야 하는 경우와 그대로 유지하는 것이 유리한 경우의 차이를 상세히 설명합니다. 세제 혜택과 운용 효율성을 고려해 본인의 투자 상황에 맞는 최적의 전략을 수립하는 방법을 제시하며, 무조건적인 이전보다는 자산 규모와 투자 목적에 따른 판단 기준을 명확히 제시합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 세금 혜택이 중요하지만, 매도 시 발생하는 비용과 NISA 한도 등을 종합적으로 고려하여 전략을 세우는 것이 핵심입니다.</t>
+  </si>
+  <si>
+    <t>株価が弱い今こそ未来を見てください。米国株がこれからも成長すると考える理由について徹底解説！</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>본 영상은 주가 하락기에도 불구하고 미국 주식이 장기적으로 성장할 수밖에 없는 이유를 분석합니다. 단기적인 시장 변동에 일희일비하기보다 기업의 본질적 성장성과 미국 경제의 구조적 강점을 살펴야 하며, 흔들리지 않는 장기 투자 전략의 중요성을 강조합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 시장이 약세를 보일 때일수록 감정에 휘둘리지 말고 미국 시장의 장기적 우상향 근거를 재확인하며 투자 기준을 세우는 것이 중요합니다.</t>
+  </si>
+  <si>
+    <t>イタリア2日目、日本って贅沢だった！イタリアで気づいた、日本が世界に愛される本当の理由。</t>
+  </si>
+  <si>
+    <t>Paradi Show</t>
+  </si>
+  <si>
+    <t>16:29</t>
+  </si>
+  <si>
+    <t>일본인 유튜버가 이탈리아 여행을 통해 일본의 일상적 편리함과 문화적 가치를 재발견하는 과정을 담았습니다. 메뉴판의 가독성, 대중교통의 정숙성, 공중화장실의 무료 이용 등 일본의 당연한 일상이 세계적으로는 흔치 않음을 깨달으며, 해외에서 오히려 일본 문화인 기모노가 귀하게 다뤄지는 모습에 큰 감동을 받는 내용을 다루고 있습니다.</t>
+  </si>
+  <si>
+    <t>해외여행을 통해 자신이 당연하게 여기던 환경의 고마움을 되새기고, 외부의 시선으로 자국 문화를 다시 바라보는 여행의 묘미를 느낄 수 있습니다.</t>
+  </si>
+  <si>
+    <t>【スカッと】社員旅行当日、旅行代理店が100人分ドタキャン「無視だ…」→「貧乏企業のキャンセル大成功」【漫画】【アニメ】【スカッとする話】【2ch】</t>
+  </si>
+  <si>
+    <t>トラブルバスターズ</t>
   </si>
   <si>
     <t>2026-07-05</t>
   </si>
   <si>
-    <t>15:43</t>
-  </si>
-  <si>
-    <t>본 영상은 LA 다저스의 야마모토 요시노부가 7이닝 10탈삼진 무실점이라는 압도적인 투구를 펼친 경기를 다룹니다. 사이영 상 후보급의 완벽한 피칭에 대해 현지 레전드들과 전문가들이 감탄하며 극찬하는 반응을 중심으로 분석하고, 그의 투구 폼과 구위가 리그 최고 수준임을 설명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 스포츠 분석 채널의 경우 사실관계와 의견을 구분하여 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>「翔平…息子は毎日闘っているんだ」マチャドが大谷に語った切実な願い…その後に見せた大谷翔平の思いがけない行動に誰もが胸を打たれた【海外の反応・MLB】</t>
-  </si>
-  <si>
-    <t>Lucis Valandoor</t>
-  </si>
-  <si>
-    <t>9:28</t>
-  </si>
-  <si>
-    <t>다저스와 파드리스의 치열한 경기 직후, 오타니 쇼헤이가 투병 중인 아들을 둔 마니 마차도의 고민을 듣고 보여준 따뜻한 인간적 면모를 다룬 내용입니다. 단순히 배트를 교환하는 것을 넘어 진심 어린 위로를 건넨 오타니의 행동은 동료인 무키 베츠와 클레이튼 커쇼에게도 큰 울림을 주었으며, 경기장을 넘어선 스포츠맨십의 감동적인 뒷이야기를 담고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 본 영상은 자극적인 제목과 썸네일을 활용한 감성 유도 콘텐츠로, 실제 사건의 구체적인 증거보다는 미담 위주의 흥미성 스토리텔링임을 감안하고 시청하시기 바랍니다.</t>
-  </si>
-  <si>
-    <t>【涙腺崩壊】「僕と同じだ…」白斑を隠さない日本代表・伊藤洋輝の右眉が、同じ病気を患うブラジル少年に起こした奇跡に世界中が涙を流す...</t>
-  </si>
-  <si>
-    <t>サッカー選手名鑑</t>
-  </si>
-  <si>
-    <t>10:47</t>
-  </si>
-  <si>
-    <t>본 영상은 일본 축구 국가대표 이토 히로키 선수가 가진 백반증에 대한 감동적인 이야기를 다룹니다. 자신의 피부 상태를 숨기지 않는 당당한 모습이 같은 병을 앓던 브라질 소년에게 큰 희망과 용기를 주었다는 내용을 중심으로, 경기 외적인 부분에서 선수가 세상에 끼친 긍정적인 영향력과 그에 대한 세계적인 반응을 전하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 본 영상은 자극적인 제목과 썸네일을 사용하여 조회수를 유도하는 클릭베이트 성향이 강하므로, 실질적인 경기 정보보다는 감성적인 스토리텔링 위주의 콘텐츠임을 감안하고 시청하시기 바랍니다.</t>
-  </si>
-  <si>
-    <t>여행</t>
-  </si>
-  <si>
-    <t>【スカッと】社員旅行当日、旅行代理店が100人分ドタキャン「無視だ…」→「貧乏企業のキャンセル大成功」【漫画】【アニメ】【スカッとする話】【2ch】</t>
-  </si>
-  <si>
-    <t>トラブルバスターズ</t>
-  </si>
-  <si>
     <t>19:59</t>
   </si>
   <si>
-    <t>이 영상은 회사 워크숍 당일, 여행사가 100인분의 예약을 일방적으로 취소하고 조롱한 사건을 다룹니다. 여행사의 악덕 행위에 맞서 주인공 일행이 법적 대응과 지혜로운 반격으로 업체를 몰락시키는 사이다 전개의 복수극입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 소재의 익명 커뮤니티 사연을 기반으로 한 창작 애니메이션이므로 사실관계가 확인되지 않은 허구의 이야기임을 인지하고 시청하는 것이 좋습니다.</t>
+    <t>이 영상은 회사 워크숍 당일, 여행사가 100인분의 예약을 일방적으로 취소하고 조롱한 사건을 다룹니다. 여행사의 갑질에 맞서 주인공 일행이 법적 대응과 철저한 증거 수집으로 통쾌하게 복수하여 여행사의 파산을 이끌어내는 권선징악형 사이다 만화입니다.</t>
+  </si>
+  <si>
+    <t>⚠️자극적인 갈등을 소재로 한 클릭베이트성 2ch 기반의 사이다 웹툰 영상입니다.</t>
+  </si>
+  <si>
+    <t>갈등</t>
+  </si>
+  <si>
+    <t>【緊急】橋本愛さん、パワハラ事件の発端となった"10年前のトラウマ"の内容が明らかになり大炎上...</t>
+  </si>
+  <si>
+    <t>じゃぱん応援隊</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>본 영상은 배우 하시모토 아이를 둘러싼 과거 권력형 괴롭힘 논란과 그 기원이 된 10년 전 사건에 관한 내용을 다루고 있습니다. 영상은 해당 논란의 구체적인 경위와 대중의 반응을 분석하며, 소속사의 관리 체계 및 업계 내 인권 문제를 중심으로 사건의 심각성을 짚어보고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 자극적인 제목과 클릭베이트 형식을 취하고 있으므로, 사실관계 확인을 위해 주류 언론사의 보도를 교차 검증하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>野良にVCで『ガチIGL』してみた結果【APEX LEGENDS】</t>
+  </si>
+  <si>
+    <t>NIRU</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>FPS 게임 에이펙스 레전드의 유명 스트리머 NIRU가 공방 매칭된 팀원들과 보이스 채팅을 사용해 진지하게 인게임 리더(IGL)를 수행하며 경기를 운영하는 모습을 담은 영상입니다. 뛰어난 오더 능력과 에임으로 팀의 승리를 이끄는 수준 높은 플레이 과정을 보여줍니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목은 강렬한 리더십을 강조하지만, 실제로는 숙련된 플레이어의 효율적인 오더와 상황 판단력을 배울 수 있는 실전 전략 영상입니다.</t>
+  </si>
+  <si>
+    <t>男子に「好きな女子に嫉妬する瞬間」聞いたら共感すぎたｗ</t>
+  </si>
+  <si>
+    <t>まつした</t>
+  </si>
+  <si>
+    <t>17:57</t>
+  </si>
+  <si>
+    <t>유튜버 마츠시타가 남성들을 대상으로 '좋아하는 여자에게 질투를 느끼는 순간'에 대해 인터뷰한 영상입니다. 연애 중 남성들이 느끼는 미묘한 감정과 상황을 솔직하게 담아내어 시청자들의 공감을 이끌어냅니다. 연애 심리를 이해하고 싶은 이들에게 흥미로운 통찰을 제공하며, 평소 연애 고민이 많은 시청자들과 소통하는 마츠시타 특유의 편안한 분위기가 돋보입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 질투는 상대방에 대한 깊은 관심에서 비롯되므로, 이를 잘 활용하면 관계를 더욱 깊게 만드는 신호로 삼을 수 있습니다.</t>
+  </si>
+  <si>
+    <t>사회핫이슈</t>
+  </si>
+  <si>
+    <t>「立憲よ満足した？」高市総理が全ての疑惑に明快答弁で野党大敗北！立憲議員は難癖つけ大逃亡…中傷動画やサナエトークン問題は終結か！経歴詐称と言ったひろゆきも終焉ｗ【無党派視点で論評】</t>
+  </si>
+  <si>
+    <t>無党派のうわずみ【政治】</t>
+  </si>
+  <si>
+    <t>14:39</t>
+  </si>
+  <si>
+    <t>2026년 7월 6일 참의원 결산위원회에서 다카이치 총리가 야당의 각종 의혹 제기에 명확하게 답변하며 공세를 방어한 상황을 다룹니다. 비서 진술서 제출, 경력 의혹, 사나에 토큰 문제 등을 조목조목 반박하며 야당의 주장을 무력화한 과정을 분석하고, 이 과정에서 논란을 빚은 히로유키 등 비판자들의 입장이 난처해졌음을 지적합니다.</t>
+  </si>
+  <si>
+    <t>⚠️정치적 논평 영상이므로 특정 정당이나 인물에 대한 편향된 시각이 포함될 수 있음을 유의하여 정보를 비판적으로 수용해야 합니다.</t>
+  </si>
+  <si>
+    <t>生後6ヶ月になったキャンディーの育児VIog</t>
+  </si>
+  <si>
+    <t>森ケの日常『娘』</t>
+  </si>
+  <si>
+    <t>8:10</t>
+  </si>
+  <si>
+    <t>생후 6개월을 맞이한 반려견 캔디의 성장 기록을 담은 브이로그입니다. 캔디가 건강하게 자라는 일상의 소소한 모습들을 따뜻한 시선으로 관찰하며, 가족들과 함께 보내는 평화로운 시간을 기록한 영상입니다. 귀여운 반려견의 성장기를 통해 반려동물을 키우는 행복과 일상의 소중함을 느낄 수 있습니다.</t>
+  </si>
+  <si>
+    <t>반려견의 성장 과정을 정기적으로 기록해두면 나중에 소중한 추억이 될 뿐만 아니라 건강 변화를 관찰하는 데도 큰 도움이 됩니다.</t>
   </si>
   <si>
     <t>미국</t>
   </si>
   <si>
-    <t>Reacting to INSANE Alpha Movie Reviews &amp; MEMES!🤣 | Pakistani Dhurandhar of YRF?</t>
-  </si>
-  <si>
-    <t>varun upasani</t>
-  </si>
-  <si>
-    <t>16:24</t>
-  </si>
-  <si>
-    <t>이 영상은 발리우드 YRF 스파이 유니버스의 최신작 '알파(Alpha)'를 둘러싼 뜨거운 논란과 평가를 다룹니다. 크리에이터는 영화에 쏟아지는 혹독한 비평들을 분석하고, 소셜 미디어에서 화제가 된 재미있는 밈들을 소개하며, 왜 이 영화가 팬들과 평론가들 사이에서 극명한 의견 차이를 보이고 있는지 심층적으로 논의합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 영화에 대한 주관적인 평가와 인터넷상의 밈을 다루는 엔터테인먼트 영상이므로, 실제 영화 관람 전 참고 자료로만 가볍게 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>Argentina vs Egypt Match Review | Controversy 😱 | FIFA World Cup 2026 Round of 16</t>
-  </si>
-  <si>
-    <t>Eesh Khera</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>10:06</t>
-  </si>
-  <si>
-    <t>본 영상은 2026 FIFA 월드컵 16강전 아르헨티나와 이집트의 경기를 다룬 리뷰 영상입니다. 경기 중 발생한 판정 논란과 주요 장면들을 중심으로 분석하며, 양 팀의 경기력과 결과에 대한 해설자의 견해를 전달합니다. 다만 영상 설명란과 자막은 주로 채널 홍보 및 링크 공유에 집중되어 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 해당 영상은 실제 2026 월드컵 공식 경기가 아닌 가상의 시나리오를 다루는 클릭베이트성 콘텐츠일 가능성이 높으니 정보 확인 시 유의하세요.</t>
-  </si>
-  <si>
-    <t>Europeans WEREN’T READY for July 4th Celebrations in America!  🇺🇸</t>
-  </si>
-  <si>
-    <t>More Adam Couser</t>
-  </si>
-  <si>
-    <t>본 영상은 영국 출신 유튜버 Adam Couser가 유럽인들이 미국의 7월 4일 독립기념일 축제 영상을 보고 보이는 반응을 시청하며 리액션하는 콘텐츠입니다. 미국 특유의 대규모 불꽃놀이와 축제 분위기에 감탄하는 유럽인들의 시각을 담고 있으며, 리액터 본인의 감상과 유머러스한 피드백이 주요 내용입니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 제목에서 유럽인들의 충격을 강조하지만, 실제로는 단순한 리액션 콘텐츠이므로 자극적인 제목에 현혹되지 말고 시청하는 것이 좋습니다.</t>
+    <t>Europeans LIED TO About America? Now Nobody Wants To Leave The U.S.</t>
+  </si>
+  <si>
+    <t>Europeans REACT America</t>
+  </si>
+  <si>
+    <t>19:54</t>
+  </si>
+  <si>
+    <t>이 영상은 미국에 대해 부정적인 고정관념을 가졌던 유럽인들이 2026년 월드컵을 계기로 미국을 직접 방문하며 겪는 변화를 다룹니다. 영화나 미디어로 접했던 위험하고 불친절한 미국의 이미지와 달리, 실제 방문 후 느끼는 치안의 안전함과 놀라운 환대, 그리고 긍정적인 반전 경험을 통해 그들이 미국에 대해 가졌던 편견이 어떻게 깨지는지를 생생하게 보여주는 다큐멘터리입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 미디어의 편향된 시각에 의존하기보다 직접적인 경험을 통해 국가의 실상을 파악하는 것이 중요합니다.</t>
+  </si>
+  <si>
+    <t>ARGENTINA HATERS MELTDOWN 😭 INSANE 3-2 COMEBACK! 🤯Argentina 3-2 Egypt</t>
+  </si>
+  <si>
+    <t>Offside Emotions</t>
+  </si>
+  <si>
+    <t>17:51</t>
+  </si>
+  <si>
+    <t>2026 FIFA 월드컵에서 아르헨티나가 이집트를 상대로 0-2로 뒤지던 경기를 뒤집고 3-2로 극적인 역전승을 거두었습니다. 이 영상은 아르헨티나의 놀라운 반등 과정과 결승골 장면, 그리고 이를 지켜본 팬들과 안티 팬들의 극명한 반응을 생생하게 담고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 본 영상은 경기 하이라이트보다는 팬들의 리액션과 자극적인 편집에 초점을 맞춘 콘텐츠이므로, 상세한 전술 분석보다는 감정적인 축구 커뮤니티의 분위기를 확인하는 용도로 적합합니다.</t>
+  </si>
+  <si>
+    <t>‘Menangis Bersama Messi!’ Reaksi Gila Dunia Melihat Argentina Ciptakan Comeback Ajaib di Piala Dunia</t>
+  </si>
+  <si>
+    <t>Dunia Bola IDN</t>
+  </si>
+  <si>
+    <t>8:28</t>
+  </si>
+  <si>
+    <t>본 영상은 2026 월드컵에서 아르헨티나가 보여준 극적인 역전승에 대한 전 세계의 열광적인 반응과 감동적인 현장 분위기를 조명합니다. 리오넬 메시와 아르헨티나 팀이 보여준 불굴의 정신력에 감격한 팬들의 눈물, 그리고 이번 경기를 역사상 가장 감동적인 컴백 중 하나로 평가하는 국제 언론들의 반응을 다룹니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목을 사용하는 전형적인 축구 이슈 요약 콘텐츠이므로, 팩트 체크와 함께 시청하는 것이 좋습니다.</t>
   </si>
   <si>
     <t>스캔들</t>
@@ -332,16 +587,13 @@
     <t>The Story Bee</t>
   </si>
   <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
     <t>10:33</t>
   </si>
   <si>
-    <t>이 영상은 테일러 스위프트와 트래비스 켈시의 관계 및 결혼과 관련된 논란을 다루고 있습니다. 특히 셀레나 고메즈를 포함한 유명 인사들이 비밀유지협약(NDA)을 체결했다는 주장을 중심으로, 두 사람의 사생활과 관련된 세간의 추측과 이슈를 정리하여 전달합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목과 내용이 자극적인 클릭베이트 형식을 띠고 있으므로 정보의 신뢰성을 재확인할 필요가 있습니다.</t>
+    <t>본 영상은 테일러 스위프트와 트래비스 켈시의 관계 및 결혼과 관련된 논란을 다루고 있습니다. 특히 셀레나 고메즈를 포함한 유명 인사들이 비밀유지계약(NDA) 서명 요구를 받았다는 의혹을 중심으로 연예계 이슈를 요약하여 전달합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목과 썸네일에서 강조하는 NDA 논란은 검증되지 않은 루머일 가능성이 높으므로 자극적인 클릭베이트성 콘텐츠임을 인지하고 시청해야 합니다.</t>
   </si>
   <si>
     <t>IT</t>
@@ -356,40 +608,55 @@
     <t>16:05</t>
   </si>
   <si>
-    <t>10년 전 출시된 iPhone 6s Plus 미개봉 제품을 55달러에 구매하여 현재 시점인 2026년에 사용할 가치가 있는지 검증합니다. 카메라 성능, 앱 실행 속도, 게임 구동, 3D 터치 기능 등을 테스트하며 과거의 명기가 현역으로 기능할 수 있을지 향수를 불러일으키는 리뷰를 진행합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 구매 시 저렴한 가격에 현혹되기보다는 10년이 지난 기기의 하드웨어 노후화와 최신 앱 지원 중단 가능성을 반드시 고려해야 합니다.</t>
-  </si>
-  <si>
-    <t>This Compact Moto Phone is a Gamechanger!</t>
-  </si>
-  <si>
-    <t>Sillycorns</t>
-  </si>
-  <si>
-    <t>5:06</t>
-  </si>
-  <si>
-    <t>모토로라의 새로운 콤팩트 스마트폰인 'Moto Edge 70 Neo'(글로벌 명칭 Edge 2026)를 다룹니다. 전설적인 Edge 50 Neo의 후속작으로 평가받으며, 합리적인 가격에 플래그십급 카메라 성능과 콤팩트한 디자인을 갖추어 기대를 모으고 있습니다. 다만 영상에서는 인도 출시와 관련해 해결해야 할 작은 문제점을 언급하며 시청자의 궁금증을 자극합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 영상 제목과 내용이 강력한 기대감을 유도하는 클릭베이트 성격이 있으므로, 실제 제품의 단점이나 인도 시장 출시 관련 이슈에 대해 객관적으로 확인하며 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>Flipkart GOAT Sale 2026 LIVE Deals 🐐💥| Biggest Discounts You Shouldn’t Miss 🔥🔥</t>
-  </si>
-  <si>
-    <t>besttechintelugu</t>
-  </si>
-  <si>
-    <t>14:12</t>
-  </si>
-  <si>
-    <t>이 영상은 Flipkart GOAT Sale 2026 기간 중 주목해야 할 가전 및 전자제품 주요 할인 품목들을 소개합니다. LG 및 다이킨 에어컨, 필립스와 솔라라 에어프라이어, 보트 스피커, CCTV 등 실생활에서 유용한 가성비 제품들의 구매 링크를 제공하며 시청자에게 최저가 구매 기회를 안내합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 클릭베이트 성격이 강하므로 영상 내 링크를 무조건 신뢰하기보다 실제 구매 전 타 쇼핑몰과 가격을 반드시 비교해 보시기 바랍니다.</t>
+    <t>10년 전 출시된 아이폰 6s Plus를 미개봉 상태로 구매하여 2026년 기준 성능을 재평가하는 영상입니다. 카메라는 물론 GTA San Andreas 게임 구동, 3D 터치 기능 등을 직접 테스트하며 전설적인 기기라 불리던 이 모델이 현대에도 실사용 가능한 가치를 지녔는지 냉철하게 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 10년이 지난 기기는 최신 앱 호환성이나 보안 업데이트 지원이 종료되었을 가능성이 크므로 실사용보다는 소장용으로 접근하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>The $1,000 Kids Phone... WORTH IT?</t>
+  </si>
+  <si>
+    <t>Smokin' Silicon</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>이 영상은 저가형 키즈폰을 구매하는 대신, 1,000달러 상당의 플래그십 모델인 갤럭시 S26에 내장된 키즈 모드 소프트웨어를 활용하는 것이 더 효율적인지 비교 분석합니다. 저가형 기기의 소프트웨어와 고사양 하드웨어의 결합이 자녀용 스마트폰으로서 실제 어떤 가치와 성능을 제공하는지 평가합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 고가의 플래그십 스마트폰을 자녀에게 사주는 것이 저가형 키즈폰보다 반드시 효율적이지는 않으므로, 내장된 소프트웨어의 제어 기능과 내구성을 우선적으로 고려하세요.</t>
+  </si>
+  <si>
+    <t>Unboxing Most *EXPENSIVE TOYS* From Amazon!🤑Worth ₹97,000</t>
+  </si>
+  <si>
+    <t>Dattrax</t>
+  </si>
+  <si>
+    <t>16:26</t>
+  </si>
+  <si>
+    <t>유튜버 Dattrax가 약 76,000루피 상당의 고가 아마존 장난감들을 언박싱하는 영상입니다. 프리미엄 품질을 자랑하는 고급 장난감들의 디자인과 기능을 직접 체험하며 솔직한 리뷰를 제공합니다. 제품의 포장부터 실제 작동 성능까지 상세히 살펴보고, 가격 대비 가치가 있는지 검증하며 시청자들에게 구매 결정을 돕기 위한 정보를 전달합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 고가의 장난감을 구매할 때는 제품의 실제 만족도와 품질 대비 가치를 판단하기 위해 다양한 사용기 리뷰를 먼저 확인하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>Dips Don't Last – 8 Stocks I’m Buying</t>
+  </si>
+  <si>
+    <t>BWB - Business With Brian</t>
+  </si>
+  <si>
+    <t>16:56</t>
+  </si>
+  <si>
+    <t>이 영상은 최근 AI 및 반도체 섹터의 조정이 일시적인 거품 붕괴가 아닌 장기적인 성장 과정임을 강조합니다. 마이크론의 실적을 근거로 AI 메모리 수요가 2028년까지 지속될 것으로 보며, 시장의 공포에 흔들리기보다 유망한 8개 종목을 선별하여 매수할 기회로 삼아야 한다고 설명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 시장의 단기적인 조정에 지나치게 반응하기보다 산업의 근본적인 수요와 성장 모멘텀이 유지되고 있는지를 파악하는 안목이 필요합니다.</t>
   </si>
   <si>
     <t>Investing in US stocks (Exposed)</t>
@@ -401,10 +668,10 @@
     <t>15:04</t>
   </si>
   <si>
-    <t>본 영상은 미국 주식 시장에 무작정 투자하려는 주인공을 통해 해외 투자의 현실적인 제약과 주의사항을 다룹니다. 단순히 해외 주식을 사는 것에 그치지 않고, 복잡한 세금 문제, 환율 변동성, 송금 수수료 및 국가 간 세제 차이 등 투자자가 반드시 고려해야 할 핵심 요소들을 전문가인 프라티크가 쉽고 상세하게 분석합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 미국 주식 투자는 단순히 종목 선택뿐만 아니라 양도소득세와 송금 비용 등 실질적인 수익률을 갉아먹는 비용 요소를 반드시 먼저 계산해야 합니다.</t>
+    <t>이 영상은 해외 주식 투자에 무작정 뛰어들려는 주인공을 통해 미국 주식 투자의 현실을 다룹니다. 막연한 환상과 달리 투자자가 반드시 고려해야 할 세금 문제, 환율 변동성, 투자 제한 및 숨겨진 비용 등 실질적인 위험 요소와 한계점을 전문가인 프라텍이 알기 쉽게 설명하며 안전한 시장 진입 전략을 제시합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 미국 주식 투자 시 단순히 수익률만 보지 말고, 현지 배당 소득세와 양도소득세 등 복잡한 세금 체계와 환전 수수료를 반드시 먼저 계산해야 합니다.</t>
   </si>
   <si>
     <t>Top Stocks I'm Buying For Massive Growth In July 2026</t>
@@ -416,25 +683,145 @@
     <t>15:44</t>
   </si>
   <si>
-    <t>영상은 2026년 7월 고성장이 기대되는 유망 주식을 분석합니다. 최근 시장이 공포 구간에 진입하며 주요 AI 관련주들이 10~30% 하락했으나, 이를 오히려 우량주를 저점 매수할 수 있는 좋은 투자 기회로 판단합니다. 과거 엔비디아와 마이크론 투자 성공 사례를 바탕으로 현재 시장에서 주목해야 할 AI 핵심 종목과 투자 전략을 제시합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 투자 서비스 홍보성 광고가 포함되어 있으므로, 추천 종목을 무조건 신뢰하기보다 객관적인 기업 분석 자료를 추가로 확인한 후 신중하게 투자하시기 바랍니다.</t>
-  </si>
-  <si>
-    <t>Stock Prices are Mathematically Impossible.</t>
-  </si>
-  <si>
-    <t>New Money</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>본 영상은 하워드 막스가 언급한 스페이스X, 앤스로픽, 오픈AI 등 IPO 광풍에 대해 다룹니다. 이를 단순한 손실 버블로 규정하며 가치 투자자들이 이러한 시장 상황에서 어떻게 대응해야 할지 투자 전략의 필요성을 강조합니다. 불확실한 시장 환경 속에서 성공적인 투자를 위한 원칙과 가치 평가의 중요성을 역설하며 개인 투자자를 위한 학습 방향을 제시합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 시장의 과열된 IPO 광풍에 휩쓸리지 말고 기업의 내재 가치를 면밀히 분석하는 가치 투자 원칙을 고수해야 합니다.</t>
+    <t>본 영상은 2026년 7월을 대비해 큰 폭의 성장이 기대되는 AI 관련 주식들을 추천하고 있습니다. 최근 시장의 공포 심리로 인해 우량한 AI 주식들이 10~30%가량 하락했음을 지적하며, 이를 엔비디아와 마이크론 사례처럼 저가 매수의 기회로 활용해야 한다고 강조합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 시장의 일시적인 공포 심리에 동요하기보다, 실적이 뒷받침되는 AI 핵심 주식의 하락세를 저가 매수 기회로 활용하십시오.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off-Roading Gone Wrong with @souravjvlogs </t>
+  </si>
+  <si>
+    <t>Dinesh Kirola</t>
+  </si>
+  <si>
+    <t>15:19</t>
+  </si>
+  <si>
+    <t>Dinesh Kirola와 Sourav Joshi가 함께 강력한 SUV를 타고 진흙 길과 가파른 경사면을 넘나드는 박진감 넘치는 오프로드 모험을 떠납니다. 순조롭게 진행되던 주행 도중 예기치 못한 사고와 장애물이 발생하며 위기에 직면하게 되는데, 과연 그들이 이 험난한 상황을 어떻게 극복하고 무사히 탈출할 수 있을지 보여주는 긴장감 넘치는 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 오프로드 주행은 돌발 상황이 많으므로 차량의 성능을 과신하지 말고 항상 안전 장비와 구조 대책을 마련한 뒤 도전하세요.</t>
+  </si>
+  <si>
+    <t>I Survived India's Brutal 4 Day Sleeper Train</t>
+  </si>
+  <si>
+    <t>Joe Fazer</t>
+  </si>
+  <si>
+    <t>19:02</t>
+  </si>
+  <si>
+    <t>유튜버 조 페이저가 인도에서 4일간 슬리퍼 기차를 타고 여행하며 겪은 고난과 경험을 다룬 영상입니다. 척박한 환경 속에서 장거리 기차 이동이 주는 육체적 피로와 현지 문화와의 접점을 솔직하게 담아내며, 스스로의 성장과 변화를 기록하는 그의 여행 일기 형식으로 구성되었습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 장거리 인도 기차 여행은 매우 덥고 위생이 열악할 수 있으므로, 출발 전 충분한 물과 위생 용품 및 개인 방호 수단을 철저히 준비하는 것이 필수적입니다.</t>
+  </si>
+  <si>
+    <t>24-Hour Train Travel Vlog 😍</t>
+  </si>
+  <si>
+    <t>Hammad Shafique</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>이 영상은 24시간 동안 기차를 타고 이동하는 여정을 담은 브이로그입니다. 장거리 기차 여행의 생생한 풍경과 기차 내부의 일상적인 모습을 보여주며, 여행자가 경험하는 시간의 흐름과 공간의 변화를 감성적으로 기록하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 영상 초반의 경고 문구는 과장된 면이 있으므로 실제 여행 시 안전 수칙만 준수하면 충분합니다.</t>
+  </si>
+  <si>
+    <t>Prashna Ravan Re-Arrested For 5th Time | Viral  Videos Controversy &amp; Trolls |Pawan Kalyan Case</t>
+  </si>
+  <si>
+    <t>Trolls Book 2.0</t>
+  </si>
+  <si>
+    <t>8:20</t>
+  </si>
+  <si>
+    <t>안드라프라데시의 유튜버 '프라슈나 라반(Prashna Ravan)'이 파완 칼리얀 부주지사에 대한 논란의 발언으로 5번째 재체포되는 사건을 다룹니다. 반복되는 체포와 보석 과정, 사생활 유출 논란 등으로 인해 소셜 미디어 내에서 밈과 조롱이 확산되는 정치적·사회적 파장을 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 클릭베이트와 인터넷 밈에 기반한 영상이므로 정보의 객관적 출처를 재확인하는 태도가 필요합니다.</t>
+  </si>
+  <si>
+    <t>TIKTOKER NÀY ĐÃ CHỬI CÁC YOUTUBER ROBLOX CHỈ VÌ DRAMA VỚI ROBLOX VNG??? | DRAMA WINTERGIRL 9277</t>
+  </si>
+  <si>
+    <t>Matchsd</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>이 영상은 최근 로블록스 VNG 관련 논란으로 인해 틱톡커 Wintergirl 9277이 로블록스 유튜버들을 비난하며 발생한 드라마를 요약 정리합니다. 해당 사건의 배경과 주요 갈등 양상을 다루며, 로블록스 커뮤니티 내 유저 간의 충돌과 소통 문제를 중점적으로 분석하여 시청자들에게 상황을 명확히 전달하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 자극적인 이슈를 다루고 있으므로, 특정인의 비난보다는 사건의 맥락을 객관적으로 파악하는 시각이 필요합니다.</t>
+  </si>
+  <si>
+    <t>The Emiru Files Just Got CRAZY</t>
+  </si>
+  <si>
+    <t>WestJett</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>유튜버 WestJett가 트위치 스트리머 에미루(Emiru)와 관련된 소송 및 논란, 그리고 아스몬골드(Asmongold)의 DM 유출 사건을 분석하는 영상입니다. Mizkif와 관련된 법적 공방 속에서 에미루가 겪은 의혹과 그 진실을 파헤치는 내용을 다루며, 커뮤니티 내 주요 인물들의 갈등과 폭로를 다각도로 검토하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목과 설명란에 포함된 소송 관련 내용은 다소 자극적인 클릭베이트 형식을 띠고 있으므로, 영상의 정보를 비판적으로 수용하고 공식적인 사실 관계를 먼저 확인하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>Streamers React to G2 LEGENDARY REVERSE SWEEPING TES | G2 vs TES Highlights | MSI 2026</t>
+  </si>
+  <si>
+    <t>Cat Esports</t>
+  </si>
+  <si>
+    <t>19:18</t>
+  </si>
+  <si>
+    <t>본 영상은 MSI 2026 G2 Esports와 Top Esports의 5전 3선승제 경기 하이라이트 및 유명 스트리머들의 반응을 담고 있습니다. 초반 1, 2세트를 내주며 위기에 몰렸던 G2가 압도적인 경기력을 바탕으로 전설적인 역스윕을 달성하는 극적인 과정을 다루고 있으며, 이에 대한 전문가와 스트리머들의 생생한 리액션을 함께 감상할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 실제 대회 결과가 아닌 팬 메이드 콘텐츠일 가능성이 높으므로 영상 속 대회 명칭이나 결과를 사실 확인 후 시청하시기 바랍니다.</t>
+  </si>
+  <si>
+    <t>Victory for Munnabhai Gaming Team! 😎 Bermuda Bulls vs Nexterra Ninjas | TCCL Match 4 #dfg #mbg</t>
+  </si>
+  <si>
+    <t>TELUGU ESPORTS ZONE</t>
+  </si>
+  <si>
+    <t>8:56</t>
+  </si>
+  <si>
+    <t>TCCL(Telugu Creators Cricket League) 4번째 경기에서 Munnabhai Gaming이 이끄는 Bermuda Bulls가 Nexterra Ninjas를 상대로 승리를 거두었습니다. 결승 진출을 위한 중요한 승부였던 이번 경기에서 팀의 활약과 주요 하이라이트를 통해 긴박했던 승부의 순간을 확인할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 클릭베이트 성격의 제목이나 짧은 하이라이트 영상일 경우, 전체 경기 전략보다는 주요 장면 위주로 감상하는 것이 효율적입니다.</t>
+  </si>
+  <si>
+    <t>Bu aim antrenmanı beni ŞAMPİYON yaptı...</t>
+  </si>
+  <si>
+    <t>Hellian VALORANT</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>발로란트 전문 유튜버 Hellian이 본인을 2주 만에 에임 챔피언으로 만든 독자적인 'Hellian 에임 메서드'를 소개합니다. 지루한 반복 훈련 없이 효율적으로 에임 실력을 극대화할 수 있는 핵심 노하우와 그가 사용하는 게이밍 마우스, 매크로 설정 등을 공유하며 시청자들에게 실력 향상을 위한 구체적인 가이드를 제시합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 클릭베이트 성격이 강하므로, 소개되는 특정 매크로 설정이나 마우스 도구에 의존하기보다 에임 메서드의 원리를 이해하는 데 초점을 맞추세요.</t>
   </si>
   <si>
     <t>I haven’t been honest with you guys</t>
@@ -446,25 +833,10 @@
     <t>10:14</t>
   </si>
   <si>
-    <t>영상 제작자인 Brandon Kim은 채널을 통해 그동안 시청자들에게 솔직하지 못했던 부분에 대해 고백하며 진실을 밝히겠다고 선언합니다. 구체적인 고백 내용보다는 편집자 구인 요청과 SNS 채널 홍보, 비즈니스 연락처 등 실무적인 안내 사항이 영상 설명의 핵심을 이루고 있는 것으로 보입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목과 내용이 일치하지 않는 전형적인 클릭베이트 영상이므로 실제 고백의 내용을 기대하기보다는 크리에이터의 채널 안내 사항으로 이해하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>Man pays for an expensive dinner date and gets ghosted by single mom</t>
-  </si>
-  <si>
-    <t>emilywking</t>
-  </si>
-  <si>
-    <t>17:17</t>
-  </si>
-  <si>
-    <t>한 여성이 첫 데이트에서 정성을 다한 남성과 만난 후, 남성의 과거 행적을 조사하기 위해 전처의 SNS와 법원 문서를 찾아봅니다. 이후 여성이 남성을 일방적으로 차단(Ghosting)한 사건을 두고, 진행자가 이 행동이 정당했는지에 대해 비판적인 시각으로 반응하는 영상입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 소재로 호기심을 유발하는 영상이므로, 파편화된 정보보다는 당사자 간의 소통과 관계의 맥락을 객관적으로 파악하는 비판적 시청 태도가 필요합니다.</t>
+    <t>영상 제목과 달리 영상 내에서 어떠한 심각한 고백이나 진실에 관한 내용은 다뤄지지 않습니다. 대신 영상 설명란을 통해 인스타그램 링크, 비즈니스 문의를 위한 이메일 주소, 영상에 사용된 배경 음악 정보 등을 공유하며 소통하고 있습니다. 결과적으로 해당 영상은 자극적인 제목을 사용하여 시청자의 호기심을 유발한 뒤 채널 정보를 홍보하는 전형적인 클릭베이트 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목이 지나치게 자극적이고 구체적인 내용이 설명란에 없다면 단순 채널 홍보성 콘텐츠일 가능성이 높으니 주의하세요.</t>
   </si>
   <si>
     <t>I CAUGHT ARBAZ WITH GIRL (DATING) 🤬 | MISHKAT KHAN</t>
@@ -473,19 +845,58 @@
     <t>Mishkat Khan</t>
   </si>
   <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
     <t>18:49</t>
   </si>
   <si>
-    <t>본 영상은 유튜버 미쉬캇 칸이 아르바즈의 데이트 현장을 포착했다는 설정을 담고 있으나, 영상 설명란을 통해 해당 콘텐츠가 실제 상황이 아닌 배우들에 의해 연출된 허구의 드라마임을 명시하고 있습니다. 시청자의 흥미를 유발하기 위해 갈등 상황을 극적으로 구성한 엔터테인먼트 목적의 영상입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목과 썸네일이 자극적인 클릭베이트 형식을 띠고 있으므로, 실제 상황이 아닌 연출된 콘텐츠임을 인지하고 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>라이프</t>
+    <t>본 영상은 유튜버 미슈캇 칸이 아르바즈가 다른 여성과 데이트하는 현장을 목격했다는 상황을 설정한 콘텐츠입니다. 그러나 영상 설명란에 명시된 바와 같이, 해당 내용은 실제 사건이 아닌 엔터테인먼트를 목적으로 연출된 허구의 스크립트 기반 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 이 영상은 클릭베이트 요소를 포함한 연출된 허구의 콘텐츠이므로 실제 상황으로 오해하지 않도록 주의해야 합니다.</t>
+  </si>
+  <si>
+    <t>PERIODISTA ARGENTINO DIJO QUE DETESTA A LOS MEXICANOS y recibió la RESPUESTA QUE JAMÁS IMAGINÓ</t>
+  </si>
+  <si>
+    <t>cuida tv con alex</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>한 아르헨티나 기자가 멕시코인들을 향해 혐오 발언을 쏟아내며 소셜 미디어에서 큰 논란을 일으켰습니다. 이 영상은 해당 기자의 구체적인 발언 내용과 그에 반발하는 멕시코인들의 거센 비판, 그리고 양국 간의 갈등이 디지털 공간에서 어떻게 확산하고 있는지 현상을 심층 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 갈등 구도를 강조해 조회수를 유도하는 클릭베이트 형식의 콘텐츠이므로 객관적 사실 확인에 주의가 필요합니다.</t>
+  </si>
+  <si>
+    <t>Stop these Indian Teachers...</t>
+  </si>
+  <si>
+    <t>Open Letter</t>
+  </si>
+  <si>
+    <t>16:46</t>
+  </si>
+  <si>
+    <t>본 영상은 유튜브 내 온라인 강사들이 교육자보다는 엔터테이너로서의 자극적인 콘텐츠를 생산하며 벌어지는 현상을 비판적으로 다룹니다. 강사 간의 비난, 감정 호소, 과장된 편집 등 '코칭 마피아'와 미디어의 상업적 생태계 속에서 교육의 본질이 변질되고 있는 실태를 날카롭게 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 유튜브 교육 콘텐츠가 실력보다는 조회수를 위한 자극적인 편집과 퍼포먼스에 의존하고 있을 가능성을 항상 경계해야 합니다.</t>
+  </si>
+  <si>
+    <t>Influencer Faces Backlash After Controversial Grocery Store Video Goes Viral</t>
+  </si>
+  <si>
+    <t>MARKIE</t>
+  </si>
+  <si>
+    <t>9:07</t>
+  </si>
+  <si>
+    <t>본 영상은 식료품점에서 촬영된 논란의 영상을 올린 한 인플루언서가 대중의 거센 비난을 받게 된 사건을 다룹니다. 영상에서는 해당 사건의 전말과 인플루언서의 부적절한 행동에 대한 대중의 반응을 분석하며, 시청자에게 관련 정보를 전달하고 기부를 독려하는 캠페인 정보를 공유합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 소재로 조회수를 유도하는 클릭베이트성 영상일 수 있으므로 비판적인 시각으로 소비하는 것이 좋습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">Reality of My Life Right Now…❤️‍🩹| Daily Vlog </t>
@@ -497,58 +908,166 @@
     <t>17:58</t>
   </si>
   <si>
-    <t>난디니 굴레리아의 브이로그 영상으로, 화려한 일상 뒤에 숨겨진 현실적인 모습과 감정적인 고민을 담담하게 그려내고 있습니다. 자신의 내면을 솔직하게 드러내며 구독자들과 공감대를 형성하는 일상적인 기록물입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 감성적인 제목과 썸네일로 시청자의 호기심을 유도하는 브이로그 형식을 띠고 있습니다.</t>
-  </si>
-  <si>
-    <t>Tahseen Ny Hamary Husky Dogs Sale Kar Diye🥺… Ab Uski Khair Nahi! 😡</t>
+    <t>난디니 굴레리아의 브이로그 영상으로, 화려한 일상 이면에 숨겨진 개인적인 감정과 삶의 현실적인 모습들을 담아내며 시청자와 깊은 공감을 나누는 영상입니다. 평범한 일상 속에서 겪는 고민과 소소한 행복의 순간들을 진솔하게 공유하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 감성적인 제목과 썸네일을 사용하여 시청자의 호기심을 유도하는 브이로그 형식을 취하고 있으므로, 가벼운 마음으로 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>Smartly Save Ur Money And Time With 1 Thing/ How to keep kitchen clean and organized/ kitchen tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H A Ideal Kitchen  .95k views .12 hours ago </t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>본 영상은 주방을 효율적으로 정리하고 청결하게 유지하기 위한 15가지 이상의 실용적인 생활 팁과 아이디어를 다룹니다. 기름때 제거법, 공간 활용법, 비용과 시간을 절약할 수 있는 기발한 주방 정리법 등을 소개하여 누구나 쉽게 따라 할 수 있는 살림 노하우를 제공합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 문구에 비해 실제 내용은 일반적인 주방 청소 및 정리 꿀팁 모음이므로, 실질적인 살림 정보 위주로 시청하시는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>Tree🌴 Py Charh Gya😱 Tahseen Ka Bhai Humy Blackmail Karny Lga😤</t>
   </si>
   <si>
     <t xml:space="preserve">Hammad Shafique Vlogs </t>
   </si>
   <si>
-    <t>14:42</t>
-  </si>
-  <si>
-    <t>영상은 유튜버 Hammad Shafique가 자신의 허스키 개들이 판매되었다는 소식을 접하고 겪는 갈등과 감정적 반응을 다룹니다. 제목은 자극적인 갈등을 암시하며, 실제 내용보다 시청자의 호기심을 유도하는 클릭베이트 성격의 브이로그 영상입니다. 영상 시작 전 동물 학대 방지 및 안전에 대한 경고 문구가 포함되어 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상 제목은 과장된 클릭베이트 성격이 강하므로, 자극적인 제목에 현혹되기보다 실제 영상의 흐름을 비판적으로 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>Sasu Maa Ne Di Sabko Dawat 🍛| Bharti Singh | Harssh Limbachiyaa | Golla | Yash</t>
-  </si>
-  <si>
-    <t>LOL (Life of Limbachiyaa’s)</t>
-  </si>
-  <si>
-    <t>16:37</t>
-  </si>
-  <si>
-    <t>유명 코미디언 부부인 바르티 싱과 하르쉬 림바치야가 운영하는 채널의 영상으로, 시어머니가 가족과 지인들을 위해 정성스러운 음식을 대접하는 따뜻한 일상을 담고 있습니다. 온 가족이 모여 식사를 즐기며 나누는 화기애애한 대화와 소소한 일상을 통해 유쾌한 가족애를 보여주며 시청자들에게 힐링과 즐거움을 선사하는 브이로그 콘텐츠입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 클릭베이트 성격이 강한 제목과 달리 실제 내용은 가족 간의 평범한 식사 브이로그이므로 가벼운 마음으로 시청하시는 것을 추천합니다.</t>
+    <t>11:33</t>
+  </si>
+  <si>
+    <t>해당 영상은 유튜버 Hammad Shafique의 일상 브이로그로, 타신(Tahseen)의 형제가 나무 위에 올라가 벌이는 소동과 블랙메일 시도 등 갈등 상황을 담고 있습니다. 영상은 시청자에게 동물 및 타인과의 상호작용 시 주의를 요구하며, 전반적으로 자극적인 제목과 썸네일을 통해 조회수를 유도하는 엔터테인먼트 성격의 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 썸네일로 시청자의 클릭을 유도하는 콘텐츠이므로 영상 내 갈등 상황이 다소 과장되거나 연출되었을 가능성을 인지하고 시청하세요.</t>
+  </si>
+  <si>
+    <t>일본핫이슈</t>
+  </si>
+  <si>
+    <t>Why Japan Is Creating a ‘Second Capital City’</t>
+  </si>
+  <si>
+    <t>TLDR News Global</t>
+  </si>
+  <si>
+    <t>9:31</t>
+  </si>
+  <si>
+    <t>일본 정부가 대규모 자연재해 발생 시 국가 기능이 마비되는 것을 방지하기 위해 도쿄를 대체하거나 보완할 '제2의 수도' 건립을 검토하고 있습니다. 이는 수도권 집중 현상에 따른 위험을 분산하고 행정 시스템의 지속 가능성을 확보하기 위한 전략적 구상으로, 이와 관련된 정치적, 경제적 파급 효과를 분석하는 내용입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목은 '제2의 수도'라는 자극적인 표현을 사용하지만 실제 내용은 국가 재난 대비 계획에 대한 정책 분석에 가깝습니다.</t>
+  </si>
+  <si>
+    <t>TRUMP DECLARES WAR ON ISLAMIC REPUBLIC OF JAPAN 😆 | Ceasefire Over and War starts</t>
+  </si>
+  <si>
+    <t>Career247</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>해당 영상은 제목에서 트럼프 전 대통령이 일본에 전쟁을 선포했다고 주장하며 시청자의 클릭을 유도하고 있으나, 실제 내용은 이란과의 긴장 관계 및 지정학적 이슈를 다루는 Prashant Dhawan의 정치 분석 콘텐츠입니다. 제목의 'Islamic Republic of Japan'은 현실에 존재하지 않는 명칭으로, 자극적인 클릭베이트를 통해 조회수를 확보하려는 성격이 강합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목이 극도로 자극적이거나 모순적인 정보를 담고 있다면, 이는 실제 정치적 사실보다 조회수를 노린 클릭베이트일 가능성이 매우 높으니 주의해야 합니다.</t>
+  </si>
+  <si>
+    <t>I visited Fox village 🦊II Indian in Japan II</t>
+  </si>
+  <si>
+    <t>Ajay Pandey</t>
+  </si>
+  <si>
+    <t>12:09</t>
+  </si>
+  <si>
+    <t>본 영상은 유튜버 Ajay Pandey가 일본의 유명 관광지인 여우 마을을 방문한 여행기를 담고 있습니다. 영상 설명란에는 자신의 소셜 미디어 계정과 촬영 장비에 대한 재치 있는 정보를 포함하고 있으며, 일본 여우 마을의 이색적인 풍경을 생생하게 전달합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 클릭베이트 성향의 설명란과 달리 실제 영상은 여행 브이로그 형식이므로 정보보다는 일본 여행의 분위기를 즐기려는 분들께 적합합니다.</t>
   </si>
   <si>
     <t>라이징스타</t>
   </si>
   <si>
-    <t>TIKTOK MASHUP VIRAL JUNE 2026 PHILIPPINES</t>
-  </si>
-  <si>
-    <t>Aura Mashup</t>
-  </si>
-  <si>
-    <t>11:19</t>
-  </si>
-  <si>
-    <t>본 영상은 2026년 6월 필리핀에서 유행한 틱톡 바이럴 영상들을 하나로 편집한 매시업 콘텐츠입니다. 최신 댄스 챌린지부터 재미있는 상황극까지 당시 SNS에서 화제를 모았던 트렌디한 영상들을 짧고 강렬하게 요약하여 시청자에게 최신 유행의 흐름을 빠르게 전달하는 엔터테인먼트 영상입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 제목으로 클릭을 유도하는 매시업 영상이므로 짧은 시간 안에 핵심 트렌드만 확인하는 용도로 활용하는 것이 좋습니다.</t>
+    <t>【海外の反応】「なぜ日本は黙っているのか」ウォン危機で世界中が注目した日本の異様な静けさ…その意味が判明して韓国凍りつく</t>
+  </si>
+  <si>
+    <t>日いづる国の観察日記</t>
+  </si>
+  <si>
+    <t>24:42</t>
+  </si>
+  <si>
+    <t>본 영상은 일본의 통화 가치 하락이나 경제적 상황에 대한 외부 반응을 다루는 자극적인 형식의 콘텐츠로 추정됩니다. 특히 한국의 원화 위기 상황에서 일본이 침묵을 지키는 이유를 다루며 일본인의 본성이나 외국인 유학생이 겪은 충격적인 사건 등 갈등 요소를 강조하여 시청자의 호기심을 유발하고 있습니다. 전형적인 해외 반응 소재의 유튜브 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목으로 클릭을 유도하는 채널이므로 정보의 객관성보다는 엔터테인먼트적인 측면으로 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>【海外の反応】「断交すれば日本が困る！」韓国で断交支持が1ヶ月で18ポイント急増→データ研究員が暴いた衝撃の真実に韓国が凍りついた</t>
+  </si>
+  <si>
+    <t>絆ストーリーテリング工房</t>
+  </si>
+  <si>
+    <t>25:43</t>
+  </si>
+  <si>
+    <t>본 영상은 한일 관계와 관련된 한국 내 단교 지지 여론 변화를 다루는 자극적인 정치 분석 콘텐츠입니다. 영상은 데이터 연구원의 주장을 빌려 한국 내 단교 찬성 여론이 급증했다는 수치를 제시하며, 이것이 한국 사회에 미칠 영향과 진실에 대해 논합니다. 표면적으로는 객관적 분석을 표방하지만, 특정 정치적 관점을 강조하는 전형적인 유튜브 이슈 몰이형 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 자극적인 제목과 썸네일을 활용한 클릭베이트 요소가 강하므로, 제시된 통계 수치나 주장의 출처를 반드시 교차 검증하는 태도가 필요합니다.</t>
+  </si>
+  <si>
+    <t>VIRAL‼️ CEWE YANG KALIAN TUNGGU2 LIVE GAPAKE ARMOR KALI INI DENGAN DASTER KUNINGNYA 😍</t>
+  </si>
+  <si>
+    <t>CuciMata</t>
+  </si>
+  <si>
+    <t>4:29</t>
+  </si>
+  <si>
+    <t>해당 영상은 라이브 스트리밍 플랫폼에서 노란색 원피스(다스테르)를 입고 시청자와 소통하는 여성 BJ의 모습을 담고 있습니다. '아머(보호장구)를 착용하지 않았다'는 제목의 표현은 노출도가 높은 의상을 강조하는 클릭베이트성 문구이며, 주로 미모를 부각하는 영상 편집 방식을 취하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목으로 시청자의 클릭을 유도하는 콘텐츠이므로 과도한 기대는 지양하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>09 July 2026 | Aaj Ki 50 Badi Khabrein | Top 50 Breaking News Today | Ravish Kumar Prime Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same Side News </t>
+  </si>
+  <si>
+    <t>8:29</t>
+  </si>
+  <si>
+    <t>2026년 7월 9일 자 '라비쉬 쿠마르 프라임 타임' 뉴스 채널의 요약본입니다. 모디 총리, 라훌 간디, 요기 아디티아나트 등 인도 주요 정치인의 행보와 관련된 50가지 핵심 뉴스를 다룹니다. 인도의 정치 상황과 당일의 주요 현안을 한눈에 파악할 수 있는 브리핑 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 해당 영상은 조회수를 겨냥한 자극적인 해시태그를 다수 포함하고 있으므로, 뉴스 출처를 반드시 교차 검증하여 객관적인 사실을 확인하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>TIKTOK MASHUP VIRAL July 2026 PHILIPPINES</t>
+  </si>
+  <si>
+    <t>Angela Mashup</t>
+  </si>
+  <si>
+    <t>7:05</t>
+  </si>
+  <si>
+    <t>이 영상은 필리핀 지역에서 2026년 7월 기준으로 유행하는 틱톡의 바이럴 영상들을 하나로 편집한 매쉬업 콘텐츠입니다. 최신 댄스 챌린지, 유머러스한 스케치 영상 등 소셜 미디어상에서 큰 화제를 모은 트렌디한 순간들을 한데 모아 시청자들에게 짧은 시간 동안 최신 유행을 빠르게 전달하는 구성을 취하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목으로 클릭을 유도하는 콘텐츠이므로 유행하는 밈을 빠르게 확인하는 용도로만 가볍게 시청하시길 바랍니다.</t>
   </si>
 </sst>
 </file>
@@ -935,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -1020,22 +1539,22 @@
         <v>24</v>
       </c>
       <c r="I2" s="3">
-        <v>176210</v>
+        <v>178570</v>
       </c>
       <c r="J2" s="3">
-        <v>3624</v>
+        <v>3700</v>
       </c>
       <c r="K2" s="3">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L2" s="3">
-        <v>28837</v>
+        <v>25746</v>
       </c>
       <c r="M2" s="3">
-        <v>1680</v>
+        <v>1700</v>
       </c>
       <c r="N2" s="4">
-        <v>104.89</v>
+        <v>105.04</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>25</v>
@@ -1070,34 +1589,34 @@
         <v>30</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="3">
+        <v>128435</v>
+      </c>
+      <c r="J3" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K3" s="3">
+        <v>385</v>
+      </c>
+      <c r="L3" s="3">
+        <v>20131</v>
+      </c>
+      <c r="M3" s="3">
+        <v>10600</v>
+      </c>
+      <c r="N3" s="4">
+        <v>12.12</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="3">
-        <v>666781</v>
-      </c>
-      <c r="J3" s="3">
-        <v>5881</v>
-      </c>
-      <c r="K3" s="3">
-        <v>533</v>
-      </c>
-      <c r="L3" s="3">
-        <v>66848</v>
-      </c>
-      <c r="M3" s="3">
-        <v>37500</v>
-      </c>
-      <c r="N3" s="4">
-        <v>17.78</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>27</v>
@@ -1120,34 +1639,34 @@
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I4" s="3">
-        <v>123530</v>
+        <v>333627</v>
       </c>
       <c r="J4" s="3">
-        <v>2235</v>
+        <v>7447</v>
       </c>
       <c r="K4" s="3">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="L4" s="3">
-        <v>21986</v>
+        <v>41869</v>
       </c>
       <c r="M4" s="3">
-        <v>10600</v>
+        <v>168000</v>
       </c>
       <c r="N4" s="4">
-        <v>11.65</v>
+        <v>1.99</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>38</v>
@@ -1188,22 +1707,22 @@
         <v>43</v>
       </c>
       <c r="I5" s="3">
-        <v>367425</v>
+        <v>381004</v>
       </c>
       <c r="J5" s="3">
-        <v>6994</v>
+        <v>7190</v>
       </c>
       <c r="K5" s="3">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="L5" s="3">
-        <v>59843</v>
+        <v>54886</v>
       </c>
       <c r="M5" s="3">
         <v>140000</v>
       </c>
       <c r="N5" s="4">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>44</v>
@@ -1238,34 +1757,34 @@
         <v>47</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I6" s="3">
-        <v>112881</v>
+        <v>145911</v>
       </c>
       <c r="J6" s="3">
-        <v>3258</v>
+        <v>4570</v>
       </c>
       <c r="K6" s="3">
-        <v>113</v>
+        <v>528</v>
       </c>
       <c r="L6" s="3">
-        <v>14783</v>
+        <v>33970</v>
       </c>
       <c r="M6" s="3">
-        <v>302000</v>
+        <v>659000</v>
       </c>
       <c r="N6" s="4">
-        <v>0.37</v>
+        <v>0.22</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>27</v>
@@ -1288,40 +1807,40 @@
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I7" s="3">
-        <v>109554</v>
+        <v>152174</v>
       </c>
       <c r="J7" s="3">
-        <v>1252</v>
+        <v>4144</v>
       </c>
       <c r="K7" s="3">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="L7" s="3">
-        <v>11116</v>
+        <v>20167</v>
       </c>
       <c r="M7" s="3">
-        <v>508000</v>
+        <v>832000</v>
       </c>
       <c r="N7" s="4">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>27</v>
@@ -1338,40 +1857,40 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>60</v>
       </c>
       <c r="I8" s="3">
-        <v>171595</v>
+        <v>112515</v>
       </c>
       <c r="J8" s="3">
-        <v>2227</v>
+        <v>3564</v>
       </c>
       <c r="K8" s="3">
-        <v>116</v>
+        <v>487</v>
       </c>
       <c r="L8" s="3">
-        <v>19318</v>
+        <v>18442</v>
       </c>
       <c r="M8" s="3">
-        <v>319000</v>
+        <v>25500</v>
       </c>
       <c r="N8" s="4">
-        <v>0.54</v>
+        <v>4.41</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>61</v>
@@ -1391,49 +1910,49 @@
         <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="I9" s="3">
+        <v>158404</v>
+      </c>
+      <c r="J9" s="3">
+        <v>6043</v>
+      </c>
+      <c r="K9" s="3">
+        <v>382</v>
+      </c>
+      <c r="L9" s="3">
+        <v>24723</v>
+      </c>
+      <c r="M9" s="3">
+        <v>68800</v>
+      </c>
+      <c r="N9" s="4">
+        <v>2.3</v>
+      </c>
+      <c r="O9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="P9" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="I9" s="3">
-        <v>101796</v>
-      </c>
-      <c r="J9" s="3">
-        <v>653</v>
-      </c>
-      <c r="K9" s="3">
-        <v>42</v>
-      </c>
-      <c r="L9" s="3">
-        <v>11467</v>
-      </c>
-      <c r="M9" s="3">
-        <v>711</v>
-      </c>
-      <c r="N9" s="4">
-        <v>143.17</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>27</v>
@@ -1447,49 +1966,49 @@
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="3">
+        <v>274458</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5355</v>
+      </c>
+      <c r="K10" s="3">
+        <v>647</v>
+      </c>
+      <c r="L10" s="3">
+        <v>72446</v>
+      </c>
+      <c r="M10" s="3">
+        <v>430000</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0.64</v>
+      </c>
+      <c r="O10" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="I10" s="3">
-        <v>101208</v>
-      </c>
-      <c r="J10" s="3">
-        <v>756</v>
-      </c>
-      <c r="K10" s="3">
-        <v>18</v>
-      </c>
-      <c r="L10" s="3">
-        <v>9304</v>
-      </c>
-      <c r="M10" s="3">
-        <v>2190</v>
-      </c>
-      <c r="N10" s="4">
-        <v>46.21</v>
-      </c>
-      <c r="O10" s="5" t="s">
+      <c r="P10" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>27</v>
@@ -1503,13 +2022,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>75</v>
@@ -1518,28 +2037,28 @@
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>77</v>
       </c>
       <c r="I11" s="3">
-        <v>343427</v>
+        <v>149073</v>
       </c>
       <c r="J11" s="3">
-        <v>1632</v>
+        <v>1895</v>
       </c>
       <c r="K11" s="3">
-        <v>175</v>
+        <v>231</v>
       </c>
       <c r="L11" s="3">
-        <v>33958</v>
+        <v>19385</v>
       </c>
       <c r="M11" s="3">
-        <v>16100</v>
+        <v>1020000</v>
       </c>
       <c r="N11" s="4">
-        <v>21.33</v>
+        <v>0.15</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>78</v>
@@ -1559,7 +2078,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>80</v>
@@ -1574,28 +2093,28 @@
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>83</v>
       </c>
       <c r="I12" s="3">
-        <v>339465</v>
+        <v>174106</v>
       </c>
       <c r="J12" s="3">
-        <v>4666</v>
+        <v>2244</v>
       </c>
       <c r="K12" s="3">
-        <v>735</v>
+        <v>116</v>
       </c>
       <c r="L12" s="3">
-        <v>48265</v>
+        <v>18067</v>
       </c>
       <c r="M12" s="3">
-        <v>690000</v>
+        <v>319000</v>
       </c>
       <c r="N12" s="4">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="O12" s="5" t="s">
         <v>84</v>
@@ -1615,10 +2134,10 @@
         <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
@@ -1630,28 +2149,28 @@
         <v>88</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I13" s="3">
-        <v>226064</v>
+        <v>101340</v>
       </c>
       <c r="J13" s="3">
-        <v>9382</v>
+        <v>2257</v>
       </c>
       <c r="K13" s="3">
-        <v>821</v>
+        <v>629</v>
       </c>
       <c r="L13" s="3">
-        <v>42625</v>
+        <v>16608</v>
       </c>
       <c r="M13" s="3">
-        <v>142000</v>
+        <v>9050</v>
       </c>
       <c r="N13" s="4">
-        <v>1.59</v>
+        <v>11.2</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>90</v>
@@ -1671,10 +2190,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
@@ -1686,34 +2205,34 @@
         <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="3">
+        <v>452442</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6878</v>
+      </c>
+      <c r="K14" s="3">
+        <v>436</v>
+      </c>
+      <c r="L14" s="3">
+        <v>68747</v>
+      </c>
+      <c r="M14" s="3">
+        <v>339000</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1.33</v>
+      </c>
+      <c r="O14" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="I14" s="3">
-        <v>108683</v>
-      </c>
-      <c r="J14" s="3">
-        <v>2038</v>
-      </c>
-      <c r="K14" s="3">
-        <v>868</v>
-      </c>
-      <c r="L14" s="3">
-        <v>35690</v>
-      </c>
-      <c r="M14" s="3">
-        <v>74900</v>
-      </c>
-      <c r="N14" s="4">
-        <v>1.45</v>
-      </c>
-      <c r="O14" s="5" t="s">
+      <c r="P14" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>27</v>
@@ -1727,43 +2246,43 @@
         <v>18</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="I15" s="3">
-        <v>361177</v>
+        <v>264992</v>
       </c>
       <c r="J15" s="3">
-        <v>21200</v>
+        <v>10670</v>
       </c>
       <c r="K15" s="3">
-        <v>2860</v>
+        <v>990</v>
       </c>
       <c r="L15" s="3">
-        <v>96374</v>
+        <v>144606</v>
       </c>
       <c r="M15" s="3">
-        <v>339000</v>
+        <v>208000</v>
       </c>
       <c r="N15" s="4">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>100</v>
@@ -1783,10 +2302,10 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
@@ -1798,34 +2317,34 @@
         <v>104</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="3">
+        <v>105506</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1136</v>
+      </c>
+      <c r="K16" s="3">
+        <v>85</v>
+      </c>
+      <c r="L16" s="3">
+        <v>12981</v>
+      </c>
+      <c r="M16" s="3">
+        <v>2090</v>
+      </c>
+      <c r="N16" s="4">
+        <v>50.48</v>
+      </c>
+      <c r="O16" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="I16" s="3">
-        <v>131931</v>
-      </c>
-      <c r="J16" s="3">
-        <v>4649</v>
-      </c>
-      <c r="K16" s="3">
-        <v>172</v>
-      </c>
-      <c r="L16" s="3">
-        <v>31530</v>
-      </c>
-      <c r="M16" s="3">
-        <v>181000</v>
-      </c>
-      <c r="N16" s="4">
-        <v>0.73</v>
-      </c>
-      <c r="O16" s="5" t="s">
+      <c r="P16" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>27</v>
@@ -1839,49 +2358,49 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="G17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="I17" s="3">
+        <v>153470</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1036</v>
+      </c>
+      <c r="K17" s="3">
+        <v>73</v>
+      </c>
+      <c r="L17" s="3">
+        <v>21178</v>
+      </c>
+      <c r="M17" s="3">
+        <v>10100</v>
+      </c>
+      <c r="N17" s="4">
+        <v>15.2</v>
+      </c>
+      <c r="O17" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="P17" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="I17" s="3">
-        <v>120673</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5932</v>
-      </c>
-      <c r="K17" s="3">
-        <v>255</v>
-      </c>
-      <c r="L17" s="3">
-        <v>24228</v>
-      </c>
-      <c r="M17" s="3">
-        <v>121000</v>
-      </c>
-      <c r="N17" s="4">
-        <v>1</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>27</v>
@@ -1895,49 +2414,49 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="D18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="I18" s="3">
+        <v>120649</v>
+      </c>
+      <c r="J18" s="3">
+        <v>667</v>
+      </c>
+      <c r="K18" s="3">
+        <v>74</v>
+      </c>
+      <c r="L18" s="3">
+        <v>12927</v>
+      </c>
+      <c r="M18" s="3">
+        <v>15000</v>
+      </c>
+      <c r="N18" s="4">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="O18" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="P18" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="I18" s="3">
-        <v>246444</v>
-      </c>
-      <c r="J18" s="3">
-        <v>5082</v>
-      </c>
-      <c r="K18" s="3">
-        <v>663</v>
-      </c>
-      <c r="L18" s="3">
-        <v>38895</v>
-      </c>
-      <c r="M18" s="3">
-        <v>720000</v>
-      </c>
-      <c r="N18" s="4">
-        <v>0.34</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="P18" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>27</v>
@@ -1951,49 +2470,49 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="D19" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="I19" s="3">
+        <v>364222</v>
+      </c>
+      <c r="J19" s="3">
+        <v>5434</v>
+      </c>
+      <c r="K19" s="3">
+        <v>437</v>
+      </c>
+      <c r="L19" s="3">
+        <v>56168</v>
+      </c>
+      <c r="M19" s="3">
+        <v>504000</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="O19" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="2" t="s">
+      <c r="P19" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="I19" s="3">
-        <v>102297</v>
-      </c>
-      <c r="J19" s="3">
-        <v>2773</v>
-      </c>
-      <c r="K19" s="3">
-        <v>171</v>
-      </c>
-      <c r="L19" s="3">
-        <v>14083</v>
-      </c>
-      <c r="M19" s="3">
-        <v>387000</v>
-      </c>
-      <c r="N19" s="4">
-        <v>0.26</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="P19" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>27</v>
@@ -2007,49 +2526,49 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H20" s="2" t="s">
+      <c r="I20" s="3">
+        <v>172807</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2287</v>
+      </c>
+      <c r="K20" s="3">
+        <v>232</v>
+      </c>
+      <c r="L20" s="3">
+        <v>30471</v>
+      </c>
+      <c r="M20" s="3">
+        <v>433000</v>
+      </c>
+      <c r="N20" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="O20" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I20" s="3">
-        <v>268221</v>
-      </c>
-      <c r="J20" s="3">
-        <v>8628</v>
-      </c>
-      <c r="K20" s="3">
-        <v>626</v>
-      </c>
-      <c r="L20" s="3">
-        <v>42614</v>
-      </c>
-      <c r="M20" s="3">
-        <v>797000</v>
-      </c>
-      <c r="N20" s="4">
-        <v>0.34</v>
-      </c>
-      <c r="O20" s="5" t="s">
+      <c r="P20" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="P20" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>27</v>
@@ -2063,49 +2582,49 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="I21" s="3">
+        <v>140394</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K21" s="3">
+        <v>42</v>
+      </c>
+      <c r="L21" s="3">
+        <v>15435</v>
+      </c>
+      <c r="M21" s="3">
+        <v>433000</v>
+      </c>
+      <c r="N21" s="4">
+        <v>0.32</v>
+      </c>
+      <c r="O21" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H21" s="2" t="s">
+      <c r="P21" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="I21" s="3">
-        <v>148648</v>
-      </c>
-      <c r="J21" s="3">
-        <v>6970</v>
-      </c>
-      <c r="K21" s="3">
-        <v>654</v>
-      </c>
-      <c r="L21" s="3">
-        <v>48438</v>
-      </c>
-      <c r="M21" s="3">
-        <v>648000</v>
-      </c>
-      <c r="N21" s="4">
-        <v>0.23</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="P21" s="5" t="s">
-        <v>134</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>27</v>
@@ -2119,49 +2638,49 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D22" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="I22" s="3">
+        <v>678064</v>
+      </c>
+      <c r="J22" s="3">
+        <v>8257</v>
+      </c>
+      <c r="K22" s="3">
+        <v>366</v>
+      </c>
+      <c r="L22" s="3">
+        <v>69568</v>
+      </c>
+      <c r="M22" s="3">
+        <v>239000</v>
+      </c>
+      <c r="N22" s="4">
+        <v>2.84</v>
+      </c>
+      <c r="O22" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="2" t="s">
+      <c r="P22" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100876</v>
-      </c>
-      <c r="J22" s="3">
-        <v>2429</v>
-      </c>
-      <c r="K22" s="3">
-        <v>231</v>
-      </c>
-      <c r="L22" s="3">
-        <v>18993</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1090000</v>
-      </c>
-      <c r="N22" s="4">
-        <v>0.09</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>27</v>
@@ -2175,49 +2694,49 @@
         <v>18</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" s="2" t="s">
+      <c r="I23" s="3">
+        <v>352176</v>
+      </c>
+      <c r="J23" s="3">
+        <v>4731</v>
+      </c>
+      <c r="K23" s="3">
+        <v>737</v>
+      </c>
+      <c r="L23" s="3">
+        <v>44975</v>
+      </c>
+      <c r="M23" s="3">
+        <v>690000</v>
+      </c>
+      <c r="N23" s="4">
+        <v>0.51</v>
+      </c>
+      <c r="O23" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="I23" s="3">
-        <v>143736</v>
-      </c>
-      <c r="J23" s="3">
-        <v>6219</v>
-      </c>
-      <c r="K23" s="3">
-        <v>389</v>
-      </c>
-      <c r="L23" s="3">
-        <v>27622</v>
-      </c>
-      <c r="M23" s="3">
-        <v>195000</v>
-      </c>
-      <c r="N23" s="4">
-        <v>0.74</v>
-      </c>
-      <c r="O23" s="5" t="s">
+      <c r="P23" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="Q23" s="2" t="s">
         <v>27</v>
@@ -2231,13 +2750,13 @@
         <v>18</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="D24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>145</v>
@@ -2246,28 +2765,28 @@
         <v>146</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>147</v>
       </c>
       <c r="I24" s="3">
-        <v>319154</v>
+        <v>869290</v>
       </c>
       <c r="J24" s="3">
-        <v>16608</v>
+        <v>12675</v>
       </c>
       <c r="K24" s="3">
-        <v>6572</v>
+        <v>2864</v>
       </c>
       <c r="L24" s="3">
-        <v>106826</v>
+        <v>130578</v>
       </c>
       <c r="M24" s="3">
-        <v>1000000</v>
+        <v>47200</v>
       </c>
       <c r="N24" s="4">
-        <v>0.32</v>
+        <v>18.42</v>
       </c>
       <c r="O24" s="5" t="s">
         <v>148</v>
@@ -2287,13 +2806,13 @@
         <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>150</v>
@@ -2302,34 +2821,34 @@
         <v>151</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="I25" s="3">
+        <v>132858</v>
+      </c>
+      <c r="J25" s="3">
+        <v>2095</v>
+      </c>
+      <c r="K25" s="3">
+        <v>103</v>
+      </c>
+      <c r="L25" s="3">
+        <v>14588</v>
+      </c>
+      <c r="M25" s="3">
+        <v>981000</v>
+      </c>
+      <c r="N25" s="4">
+        <v>0.14</v>
+      </c>
+      <c r="O25" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="I25" s="3">
-        <v>507131</v>
-      </c>
-      <c r="J25" s="3">
-        <v>12214</v>
-      </c>
-      <c r="K25" s="3">
-        <v>1777</v>
-      </c>
-      <c r="L25" s="3">
-        <v>235598</v>
-      </c>
-      <c r="M25" s="3">
-        <v>3810000</v>
-      </c>
-      <c r="N25" s="4">
-        <v>0.13</v>
-      </c>
-      <c r="O25" s="5" t="s">
+      <c r="P25" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="P25" s="5" t="s">
-        <v>155</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>27</v>
@@ -2343,49 +2862,49 @@
         <v>18</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="I26" s="3">
+        <v>105215</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1981</v>
+      </c>
+      <c r="K26" s="3">
+        <v>122</v>
+      </c>
+      <c r="L26" s="3">
+        <v>15045</v>
+      </c>
+      <c r="M26" s="3">
+        <v>1120000</v>
+      </c>
+      <c r="N26" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="O26" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" s="2" t="s">
+      <c r="P26" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="I26" s="3">
-        <v>114144</v>
-      </c>
-      <c r="J26" s="3">
-        <v>2920</v>
-      </c>
-      <c r="K26" s="3">
-        <v>206</v>
-      </c>
-      <c r="L26" s="3">
-        <v>29967</v>
-      </c>
-      <c r="M26" s="3">
-        <v>4350</v>
-      </c>
-      <c r="N26" s="4">
-        <v>26.24</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="P26" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="Q26" s="2" t="s">
         <v>27</v>
@@ -2399,49 +2918,49 @@
         <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="2" t="s">
+      <c r="I27" s="3">
+        <v>152133</v>
+      </c>
+      <c r="J27" s="3">
+        <v>2112</v>
+      </c>
+      <c r="K27" s="3">
+        <v>566</v>
+      </c>
+      <c r="L27" s="3">
+        <v>23639</v>
+      </c>
+      <c r="M27" s="3">
+        <v>4040</v>
+      </c>
+      <c r="N27" s="4">
+        <v>37.66</v>
+      </c>
+      <c r="O27" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="I27" s="3">
-        <v>460002</v>
-      </c>
-      <c r="J27" s="3">
-        <v>9087</v>
-      </c>
-      <c r="K27" s="3">
-        <v>532</v>
-      </c>
-      <c r="L27" s="3">
-        <v>55856</v>
-      </c>
-      <c r="M27" s="3">
-        <v>241000</v>
-      </c>
-      <c r="N27" s="4">
-        <v>1.91</v>
-      </c>
-      <c r="O27" s="5" t="s">
+      <c r="P27" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="P27" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="Q27" s="2" t="s">
         <v>27</v>
@@ -2455,54 +2974,1734 @@
         <v>18</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I28" s="3">
+        <v>121960</v>
+      </c>
+      <c r="J28" s="3">
+        <v>2536</v>
+      </c>
+      <c r="K28" s="3">
+        <v>109</v>
+      </c>
+      <c r="L28" s="3">
+        <v>30030</v>
+      </c>
+      <c r="M28" s="3">
+        <v>436000</v>
+      </c>
+      <c r="N28" s="4">
+        <v>0.28</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I29" s="3">
+        <v>247025</v>
+      </c>
+      <c r="J29" s="3">
+        <v>12230</v>
+      </c>
+      <c r="K29" s="3">
+        <v>1688</v>
+      </c>
+      <c r="L29" s="3">
+        <v>120700</v>
+      </c>
+      <c r="M29" s="3">
+        <v>2460</v>
+      </c>
+      <c r="N29" s="4">
+        <v>100.42</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I30" s="3">
+        <v>738043</v>
+      </c>
+      <c r="J30" s="3">
+        <v>12838</v>
+      </c>
+      <c r="K30" s="3">
+        <v>2949</v>
+      </c>
+      <c r="L30" s="3">
+        <v>149645</v>
+      </c>
+      <c r="M30" s="3">
+        <v>18500</v>
+      </c>
+      <c r="N30" s="4">
+        <v>39.89</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="P30" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="2">
         <v>3</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I28" s="3">
-        <v>1290217</v>
-      </c>
-      <c r="J28" s="3">
-        <v>35935</v>
-      </c>
-      <c r="K28" s="3">
-        <v>589</v>
-      </c>
-      <c r="L28" s="3">
-        <v>166413</v>
-      </c>
-      <c r="M28" s="3">
-        <v>9110000</v>
-      </c>
-      <c r="N28" s="4">
-        <v>0.14</v>
-      </c>
-      <c r="O28" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="P28" s="5" t="s">
+      <c r="E31" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I31" s="3">
+        <v>153811</v>
+      </c>
+      <c r="J31" s="3">
+        <v>1346</v>
+      </c>
+      <c r="K31" s="3">
+        <v>604</v>
+      </c>
+      <c r="L31" s="3">
+        <v>28338</v>
+      </c>
+      <c r="M31" s="3">
+        <v>28500</v>
+      </c>
+      <c r="N31" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="P31" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="Q28" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R28" s="2" t="s">
+      <c r="C32" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I32" s="3">
+        <v>141616</v>
+      </c>
+      <c r="J32" s="3">
+        <v>4904</v>
+      </c>
+      <c r="K32" s="3">
+        <v>177</v>
+      </c>
+      <c r="L32" s="3">
+        <v>28276</v>
+      </c>
+      <c r="M32" s="3">
+        <v>181000</v>
+      </c>
+      <c r="N32" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="P32" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I33" s="3">
+        <v>130438</v>
+      </c>
+      <c r="J33" s="3">
+        <v>6258</v>
+      </c>
+      <c r="K33" s="3">
+        <v>260</v>
+      </c>
+      <c r="L33" s="3">
+        <v>23518</v>
+      </c>
+      <c r="M33" s="3">
+        <v>122000</v>
+      </c>
+      <c r="N33" s="4">
+        <v>1.07</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I34" s="3">
+        <v>114227</v>
+      </c>
+      <c r="J34" s="3">
+        <v>3132</v>
+      </c>
+      <c r="K34" s="3">
+        <v>255</v>
+      </c>
+      <c r="L34" s="3">
+        <v>17787</v>
+      </c>
+      <c r="M34" s="3">
+        <v>223000</v>
+      </c>
+      <c r="N34" s="4">
+        <v>0.51</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="P34" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I35" s="3">
+        <v>306679</v>
+      </c>
+      <c r="J35" s="3">
+        <v>14050</v>
+      </c>
+      <c r="K35" s="3">
+        <v>456</v>
+      </c>
+      <c r="L35" s="3">
+        <v>60050</v>
+      </c>
+      <c r="M35" s="3">
+        <v>650000</v>
+      </c>
+      <c r="N35" s="4">
+        <v>0.47</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="P35" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="I36" s="3">
+        <v>160977</v>
+      </c>
+      <c r="J36" s="3">
+        <v>6773</v>
+      </c>
+      <c r="K36" s="3">
+        <v>539</v>
+      </c>
+      <c r="L36" s="3">
+        <v>60330</v>
+      </c>
+      <c r="M36" s="3">
+        <v>416000</v>
+      </c>
+      <c r="N36" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="P36" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I37" s="3">
+        <v>274839</v>
+      </c>
+      <c r="J37" s="3">
+        <v>8782</v>
+      </c>
+      <c r="K37" s="3">
+        <v>630</v>
+      </c>
+      <c r="L37" s="3">
+        <v>40165</v>
+      </c>
+      <c r="M37" s="3">
+        <v>798000</v>
+      </c>
+      <c r="N37" s="4">
+        <v>0.34</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="P37" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="2">
+        <v>3</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I38" s="3">
+        <v>161990</v>
+      </c>
+      <c r="J38" s="3">
+        <v>7344</v>
+      </c>
+      <c r="K38" s="3">
+        <v>763</v>
+      </c>
+      <c r="L38" s="3">
+        <v>43853</v>
+      </c>
+      <c r="M38" s="3">
+        <v>648000</v>
+      </c>
+      <c r="N38" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="P38" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I39" s="3">
+        <v>292909</v>
+      </c>
+      <c r="J39" s="3">
+        <v>5779</v>
+      </c>
+      <c r="K39" s="3">
+        <v>148</v>
+      </c>
+      <c r="L39" s="3">
+        <v>33951</v>
+      </c>
+      <c r="M39" s="3">
+        <v>174000</v>
+      </c>
+      <c r="N39" s="4">
+        <v>1.68</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="P39" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I40" s="3">
+        <v>915126</v>
+      </c>
+      <c r="J40" s="3">
+        <v>40727</v>
+      </c>
+      <c r="K40" s="3">
+        <v>6171</v>
+      </c>
+      <c r="L40" s="3">
+        <v>209120</v>
+      </c>
+      <c r="M40" s="3">
+        <v>2170000</v>
+      </c>
+      <c r="N40" s="4">
+        <v>0.42</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="P40" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="2">
+        <v>3</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I41" s="3">
+        <v>116558</v>
+      </c>
+      <c r="J41" s="3">
+        <v>5646</v>
+      </c>
+      <c r="K41" s="3">
+        <v>334</v>
+      </c>
+      <c r="L41" s="3">
+        <v>33119</v>
+      </c>
+      <c r="M41" s="3">
+        <v>575000</v>
+      </c>
+      <c r="N41" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="P41" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="2">
+        <v>1</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I42" s="3">
+        <v>127478</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3202</v>
+      </c>
+      <c r="K42" s="3">
+        <v>366</v>
+      </c>
+      <c r="L42" s="3">
+        <v>19255</v>
+      </c>
+      <c r="M42" s="3">
+        <v>6420</v>
+      </c>
+      <c r="N42" s="4">
+        <v>19.86</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="P42" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I43" s="3">
+        <v>136431</v>
+      </c>
+      <c r="J43" s="3">
+        <v>3734</v>
+      </c>
+      <c r="K43" s="3">
+        <v>1612</v>
+      </c>
+      <c r="L43" s="3">
+        <v>35077</v>
+      </c>
+      <c r="M43" s="3">
+        <v>41400</v>
+      </c>
+      <c r="N43" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="P43" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="2">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="I44" s="3">
+        <v>164381</v>
+      </c>
+      <c r="J44" s="3">
+        <v>11237</v>
+      </c>
+      <c r="K44" s="3">
+        <v>1389</v>
+      </c>
+      <c r="L44" s="3">
+        <v>211751</v>
+      </c>
+      <c r="M44" s="3">
+        <v>796000</v>
+      </c>
+      <c r="N44" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="P44" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D45" s="2">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I45" s="3">
+        <v>174105</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3565</v>
+      </c>
+      <c r="K45" s="3">
+        <v>208</v>
+      </c>
+      <c r="L45" s="3">
+        <v>21911</v>
+      </c>
+      <c r="M45" s="3">
+        <v>9300</v>
+      </c>
+      <c r="N45" s="4">
+        <v>18.72</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="P45" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I46" s="3">
+        <v>127819</v>
+      </c>
+      <c r="J46" s="3">
+        <v>3530</v>
+      </c>
+      <c r="K46" s="3">
+        <v>22</v>
+      </c>
+      <c r="L46" s="3">
+        <v>17287</v>
+      </c>
+      <c r="M46" s="3">
+        <v>16100</v>
+      </c>
+      <c r="N46" s="4">
+        <v>7.94</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" s="2">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I47" s="3">
+        <v>211590</v>
+      </c>
+      <c r="J47" s="3">
+        <v>15880</v>
+      </c>
+      <c r="K47" s="3">
+        <v>1059</v>
+      </c>
+      <c r="L47" s="3">
+        <v>51159</v>
+      </c>
+      <c r="M47" s="3">
+        <v>470000</v>
+      </c>
+      <c r="N47" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="P47" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D48" s="2">
+        <v>1</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I48" s="3">
+        <v>148886</v>
+      </c>
+      <c r="J48" s="3">
+        <v>6362</v>
+      </c>
+      <c r="K48" s="3">
+        <v>393</v>
+      </c>
+      <c r="L48" s="3">
+        <v>25977</v>
+      </c>
+      <c r="M48" s="3">
+        <v>195000</v>
+      </c>
+      <c r="N48" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="O48" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="P48" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I49" s="3">
+        <v>734882</v>
+      </c>
+      <c r="J49" s="3">
+        <v>15591</v>
+      </c>
+      <c r="K49" s="3">
+        <v>2236</v>
+      </c>
+      <c r="L49" s="3">
+        <v>202242</v>
+      </c>
+      <c r="M49" s="3">
+        <v>3810000</v>
+      </c>
+      <c r="N49" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="P49" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D50" s="2">
+        <v>1</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="I50" s="3">
+        <v>254936</v>
+      </c>
+      <c r="J50" s="3">
+        <v>8966</v>
+      </c>
+      <c r="K50" s="3">
+        <v>1022</v>
+      </c>
+      <c r="L50" s="3">
+        <v>73329</v>
+      </c>
+      <c r="M50" s="3">
+        <v>371000</v>
+      </c>
+      <c r="N50" s="4">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O50" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="P50" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I51" s="3">
+        <v>487851</v>
+      </c>
+      <c r="J51" s="3">
+        <v>23952</v>
+      </c>
+      <c r="K51" s="3">
+        <v>3476</v>
+      </c>
+      <c r="L51" s="3">
+        <v>113369</v>
+      </c>
+      <c r="M51" s="3">
+        <v>1310000</v>
+      </c>
+      <c r="N51" s="4">
+        <v>0.37</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="P51" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D52" s="2">
+        <v>3</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I52" s="3">
+        <v>120152</v>
+      </c>
+      <c r="J52" s="3">
+        <v>5227</v>
+      </c>
+      <c r="K52" s="3">
+        <v>1885</v>
+      </c>
+      <c r="L52" s="3">
+        <v>42028</v>
+      </c>
+      <c r="M52" s="3">
+        <v>584000</v>
+      </c>
+      <c r="N52" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="P52" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I53" s="3">
+        <v>128764</v>
+      </c>
+      <c r="J53" s="3">
+        <v>3181</v>
+      </c>
+      <c r="K53" s="3">
+        <v>227</v>
+      </c>
+      <c r="L53" s="3">
+        <v>26588</v>
+      </c>
+      <c r="M53" s="3">
+        <v>5610</v>
+      </c>
+      <c r="N53" s="4">
+        <v>22.95</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="P53" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R53" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="A54" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I54" s="3">
+        <v>180269</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1837</v>
+      </c>
+      <c r="K54" s="3">
+        <v>100</v>
+      </c>
+      <c r="L54" s="3">
+        <v>19728</v>
+      </c>
+      <c r="M54" s="3">
+        <v>39600</v>
+      </c>
+      <c r="N54" s="4">
+        <v>4.55</v>
+      </c>
+      <c r="O54" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="P54" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="A55" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D55" s="2">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="I55" s="3">
+        <v>206140</v>
+      </c>
+      <c r="J55" s="3">
+        <v>5997</v>
+      </c>
+      <c r="K55" s="3">
+        <v>235</v>
+      </c>
+      <c r="L55" s="3">
+        <v>30906</v>
+      </c>
+      <c r="M55" s="3">
+        <v>242000</v>
+      </c>
+      <c r="N55" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="O55" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="P55" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="A56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D56" s="2">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="I56" s="3">
+        <v>541129</v>
+      </c>
+      <c r="J56" s="3">
+        <v>13175</v>
+      </c>
+      <c r="K56" s="3">
+        <v>1743</v>
+      </c>
+      <c r="L56" s="3">
+        <v>93151</v>
+      </c>
+      <c r="M56" s="3">
+        <v>1140000</v>
+      </c>
+      <c r="N56" s="4">
+        <v>0.47</v>
+      </c>
+      <c r="O56" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="P56" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I57" s="3">
+        <v>502328</v>
+      </c>
+      <c r="J57" s="3">
+        <v>33411</v>
+      </c>
+      <c r="K57" s="3">
+        <v>2860</v>
+      </c>
+      <c r="L57" s="3">
+        <v>195079</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1760000</v>
+      </c>
+      <c r="N57" s="4">
+        <v>0.29</v>
+      </c>
+      <c r="O57" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="P57" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D58" s="2">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="I58" s="3">
+        <v>133968</v>
+      </c>
+      <c r="J58" s="3">
+        <v>4935</v>
+      </c>
+      <c r="K58" s="3">
+        <v>222</v>
+      </c>
+      <c r="L58" s="3">
+        <v>22354</v>
+      </c>
+      <c r="M58" s="3">
+        <v>491000</v>
+      </c>
+      <c r="N58" s="4">
+        <v>0.27</v>
+      </c>
+      <c r="O58" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="P58" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R58" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2535,6 +4734,36 @@
     <hyperlink ref="Q26" r:id="rId25"/>
     <hyperlink ref="Q27" r:id="rId26"/>
     <hyperlink ref="Q28" r:id="rId27"/>
+    <hyperlink ref="Q29" r:id="rId28"/>
+    <hyperlink ref="Q30" r:id="rId29"/>
+    <hyperlink ref="Q31" r:id="rId30"/>
+    <hyperlink ref="Q32" r:id="rId31"/>
+    <hyperlink ref="Q33" r:id="rId32"/>
+    <hyperlink ref="Q34" r:id="rId33"/>
+    <hyperlink ref="Q35" r:id="rId34"/>
+    <hyperlink ref="Q36" r:id="rId35"/>
+    <hyperlink ref="Q37" r:id="rId36"/>
+    <hyperlink ref="Q38" r:id="rId37"/>
+    <hyperlink ref="Q39" r:id="rId38"/>
+    <hyperlink ref="Q40" r:id="rId39"/>
+    <hyperlink ref="Q41" r:id="rId40"/>
+    <hyperlink ref="Q42" r:id="rId41"/>
+    <hyperlink ref="Q43" r:id="rId42"/>
+    <hyperlink ref="Q44" r:id="rId43"/>
+    <hyperlink ref="Q45" r:id="rId44"/>
+    <hyperlink ref="Q46" r:id="rId45"/>
+    <hyperlink ref="Q47" r:id="rId46"/>
+    <hyperlink ref="Q48" r:id="rId47"/>
+    <hyperlink ref="Q49" r:id="rId48"/>
+    <hyperlink ref="Q50" r:id="rId49"/>
+    <hyperlink ref="Q51" r:id="rId50"/>
+    <hyperlink ref="Q52" r:id="rId51"/>
+    <hyperlink ref="Q53" r:id="rId52"/>
+    <hyperlink ref="Q54" r:id="rId53"/>
+    <hyperlink ref="Q55" r:id="rId54"/>
+    <hyperlink ref="Q56" r:id="rId55"/>
+    <hyperlink ref="Q57" r:id="rId56"/>
+    <hyperlink ref="Q58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2542,7 +4771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -2606,60 +4835,288 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>172</v>
+        <v>325</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>326</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>174</v>
+        <v>327</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>175</v>
+        <v>328</v>
       </c>
       <c r="I2" s="3">
-        <v>98851</v>
+        <v>52644</v>
       </c>
       <c r="J2" s="3">
-        <v>236</v>
+        <v>305</v>
       </c>
       <c r="K2" s="3">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
       </c>
       <c r="M2" s="3">
-        <v>1410</v>
+        <v>98</v>
       </c>
       <c r="N2" s="4">
+        <v>537</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="O2" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="I3" s="3">
+        <v>73447</v>
+      </c>
+      <c r="J3" s="3">
+        <v>459</v>
+      </c>
+      <c r="K3" s="3">
+        <v>74</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>174</v>
+      </c>
+      <c r="N3" s="4">
+        <v>422</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I4" s="3">
+        <v>141134</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1527</v>
+      </c>
+      <c r="K4" s="3">
+        <v>78</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>1270</v>
+      </c>
+      <c r="N4" s="4">
+        <v>111</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I5" s="3">
+        <v>222704</v>
+      </c>
+      <c r="J5" s="3">
+        <v>3786</v>
+      </c>
+      <c r="K5" s="3">
+        <v>67</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>2890</v>
+      </c>
+      <c r="N5" s="4">
+        <v>77</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I6" s="3">
+        <v>78231</v>
+      </c>
+      <c r="J6" s="3">
+        <v>236</v>
+      </c>
+      <c r="K6" s="3">
+        <v>16</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1080</v>
+      </c>
+      <c r="N6" s="4">
+        <v>72</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="Q2" r:id="rId1"/>
+    <hyperlink ref="Q3" r:id="rId2"/>
+    <hyperlink ref="Q4" r:id="rId3"/>
+    <hyperlink ref="Q5" r:id="rId4"/>
+    <hyperlink ref="Q6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
